--- a/Benchmark_Comparison_GNN_vs_Baselines.xlsx
+++ b/Benchmark_Comparison_GNN_vs_Baselines.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost_Comparison" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FillRate_Comparison" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed_Stats" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost_Breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Episodes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cost_Comparison" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="FillRate_Comparison" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Detailed_Stats" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cost_Breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Raw_Episodes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Methodology" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -134,10 +134,10 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -159,16 +159,16 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -629,16 +629,16 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>11.76711598</v>
+        <v>55.2697481</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>264.2273326599999</v>
+        <v>65.73206165999999</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>262.18504354</v>
+        <v>65.7692102</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>294.1235757600001</v>
+        <v>83.12825875999999</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -652,21 +652,21 @@
           <t>1x7</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>71.59054244000001</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>105.43504684</v>
+      <c r="B7" s="7" t="n">
+        <v>73.94904883999999</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>71.54982554</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>109.94782728</v>
+        <v>71.54982554</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>116.94121104</v>
+        <v>74.44927092</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>MAPPO</t>
         </is>
       </c>
     </row>
@@ -677,16 +677,16 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>174.95273972</v>
+        <v>87.47367942</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>364.80710478</v>
+        <v>102.41096022</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>367.80324106</v>
+        <v>101.42445222</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>417.67333198</v>
+        <v>90.36350659999999</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -700,11 +700,11 @@
           <t>2x15</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>170.82634104</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>209.89549308</v>
+      <c r="B9" s="7" t="n">
+        <v>213.48660962</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>207.66048284</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>250.76989134</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>MAPPO</t>
         </is>
       </c>
     </row>
@@ -796,8 +796,8 @@
           <t>4x15</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
-        <v>56.282888</v>
+      <c r="B13" s="7" t="n">
+        <v>88.71947573999999</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>163.58476914</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>GNN-HAPPO</t>
         </is>
       </c>
     </row>
@@ -820,21 +820,21 @@
           <t>4x30</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
-        <v>332.46828218</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>431.01602148</v>
+      <c r="B14" s="7" t="n">
+        <v>142.65096726</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>116.82890448</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>411.42811356</v>
+        <v>116.82890448</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>388.3581053</v>
+        <v>128.19088714</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>MAPPO</t>
         </is>
       </c>
     </row>
@@ -844,8 +844,8 @@
           <t>4x40</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>676.8887525199999</v>
+      <c r="B15" s="7" t="n">
+        <v>742.6929709799999</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>714.7804355599999</v>
@@ -858,7 +858,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>GNN-HAPPO</t>
         </is>
       </c>
     </row>
@@ -908,20 +908,20 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>95.52536000000001</v>
+        <v>97.74202</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>76.65346</v>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>77.84826000000001</v>
+        <v>100</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>100</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>60.24364000000001</v>
+        <v>98.58438000000001</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>MAPPO</t>
         </is>
       </c>
     </row>
@@ -931,21 +931,21 @@
           <t>1x7</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
-        <v>91.67654</v>
+      <c r="B21" s="9" t="n">
+        <v>99.89196</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>78.01594</v>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>78.28578</v>
+        <v>100</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>100</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>96.2818</v>
+        <v>100</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>GNN-HAPPO</t>
+          <t>MAPPO</t>
         </is>
       </c>
     </row>
@@ -956,20 +956,20 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>86.72666</v>
+        <v>98.01527999999999</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>79.23348000000001</v>
-      </c>
-      <c r="D22" s="10" t="n">
-        <v>79.29212000000001</v>
+        <v>100</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>100</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>79.21602</v>
+        <v>100</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>MAPPO</t>
         </is>
       </c>
     </row>
@@ -979,13 +979,13 @@
           <t>2x15</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
-        <v>90.72194</v>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>78.11203999999999</v>
-      </c>
-      <c r="D23" s="10" t="n">
+      <c r="B23" s="9" t="n">
+        <v>91.2577</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>78.22596</v>
+      </c>
+      <c r="D23" s="9" t="n">
         <v>77.50592</v>
       </c>
       <c r="E23" s="11" t="n">
@@ -1003,13 +1003,13 @@
           <t>2x20</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B24" s="9" t="n">
         <v>86.81702</v>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C24" s="9" t="n">
         <v>77.64962</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="9" t="n">
         <v>77.16254000000001</v>
       </c>
       <c r="E24" s="11" t="n">
@@ -1027,13 +1027,13 @@
           <t>2x30</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B25" s="9" t="n">
         <v>82.45252000000001</v>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C25" s="9" t="n">
         <v>77.25902000000001</v>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D25" s="9" t="n">
         <v>76.85171999999999</v>
       </c>
       <c r="E25" s="11" t="n">
@@ -1051,13 +1051,13 @@
           <t>2x40</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
+      <c r="B26" s="9" t="n">
         <v>80.20660000000001</v>
       </c>
-      <c r="C26" s="10" t="n">
+      <c r="C26" s="9" t="n">
         <v>76.56368000000001</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="9" t="n">
         <v>76.2445</v>
       </c>
       <c r="E26" s="11" t="n">
@@ -1075,13 +1075,13 @@
           <t>4x15</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n">
-        <v>95.48144000000001</v>
-      </c>
-      <c r="C27" s="10" t="n">
+      <c r="B27" s="10" t="n">
+        <v>95.30121999999999</v>
+      </c>
+      <c r="C27" s="9" t="n">
         <v>80.41724000000001</v>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D27" s="9" t="n">
         <v>80.41724000000001</v>
       </c>
       <c r="E27" s="11" t="n">
@@ -1100,20 +1100,20 @@
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>90.82626</v>
-      </c>
-      <c r="C28" s="10" t="n">
-        <v>77.58844000000001</v>
-      </c>
-      <c r="D28" s="10" t="n">
-        <v>77.66758000000002</v>
+        <v>95.89005999999999</v>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>99.33788000000001</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>99.33788000000001</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>84.27312000000001</v>
+        <v>99.76740000000001</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>GNN-HAPPO</t>
         </is>
       </c>
     </row>
@@ -1123,13 +1123,13 @@
           <t>4x40</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n">
-        <v>87.71088</v>
-      </c>
-      <c r="C29" s="10" t="n">
+      <c r="B29" s="9" t="n">
+        <v>87.47286000000001</v>
+      </c>
+      <c r="C29" s="9" t="n">
         <v>77.61855999999999</v>
       </c>
-      <c r="D29" s="10" t="n">
+      <c r="D29" s="9" t="n">
         <v>77.50183999999999</v>
       </c>
       <c r="E29" s="11" t="n">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>435.079712246</v>
+        <v>426.026296054</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>407.994182748</v>
+        <v>326.8743063379999</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>410.62057798</v>
+        <v>331.0413946799999</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>375.1548303119999</v>
+        <v>291.058400246</v>
       </c>
     </row>
     <row r="35">
@@ -1200,17 +1200,17 @@
           <t>Avg Fill Rate (%)</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n">
-        <v>88.814522</v>
-      </c>
-      <c r="C35" s="10" t="n">
-        <v>77.911148</v>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>77.87775000000001</v>
+      <c r="B35" s="9" t="n">
+        <v>91.504724</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>86.70719600000001</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>86.50216400000001</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>87.14810000000003</v>
+        <v>94.98182000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1279,16 +1279,16 @@
         </is>
       </c>
       <c r="C2" s="7" t="n">
-        <v>11.76711598</v>
+        <v>55.2697481</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>294.1235757600001</v>
+        <v>83.12825875999999</v>
       </c>
       <c r="E2" s="13" t="n">
-        <v>-282.35645978</v>
+        <v>-27.85851065999999</v>
       </c>
       <c r="F2" s="14" t="n">
-        <v>-2399.538342784313</v>
+        <v>-50.40462751810514</v>
       </c>
     </row>
     <row r="3">
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>264.2273326599999</v>
+        <v>65.73206165999999</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>294.1235757600001</v>
+        <v>83.12825875999999</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>-29.89624310000008</v>
+        <v>-17.39619710000001</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>-11.31459141604767</v>
+        <v>-26.46531488694525</v>
       </c>
     </row>
     <row r="4">
@@ -1319,16 +1319,16 @@
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>262.18504354</v>
+        <v>65.7692102</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>294.1235757600001</v>
+        <v>83.12825875999999</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>-31.93853222000005</v>
+        <v>-17.35904855999999</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>-12.18167588386001</v>
+        <v>-26.39388325815716</v>
       </c>
     </row>
     <row r="5">
@@ -1343,16 +1343,16 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>71.59054244000001</v>
+        <v>73.94904883999999</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>116.94121104</v>
+        <v>74.44927092</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>-45.35066859999999</v>
+        <v>-0.5002220800000213</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>-63.3472900949289</v>
+        <v>-0.6764415335244243</v>
       </c>
     </row>
     <row r="6">
@@ -1363,16 +1363,16 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>105.43504684</v>
+        <v>71.54982554</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>116.94121104</v>
+        <v>74.44927092</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>-11.50616419999998</v>
+        <v>-2.899445380000005</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>-10.91303560329502</v>
+        <v>-4.052344444053279</v>
       </c>
     </row>
     <row r="7">
@@ -1383,16 +1383,16 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>109.94782728</v>
+        <v>71.54982554</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>116.94121104</v>
+        <v>74.44927092</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>-6.993383759999997</v>
+        <v>-2.899445380000005</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>-6.360638434618821</v>
+        <v>-4.052344444053279</v>
       </c>
     </row>
     <row r="8">
@@ -1407,16 +1407,16 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>174.95273972</v>
+        <v>87.47367942</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>417.67333198</v>
+        <v>90.36350659999999</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>-242.72059226</v>
+        <v>-2.889827179999993</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>-138.7349478770426</v>
+        <v>-3.303653395125462</v>
       </c>
     </row>
     <row r="9">
@@ -1427,16 +1427,16 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>364.80710478</v>
+        <v>102.41096022</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>417.67333198</v>
+        <v>90.36350659999999</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>-52.86622720000003</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>-14.4915563615137</v>
+        <v>12.04745362000001</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>11.76383230283124</v>
       </c>
     </row>
     <row r="10">
@@ -1447,16 +1447,16 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>367.80324106</v>
+        <v>101.42445222</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>417.67333198</v>
+        <v>90.36350659999999</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>-49.87009091999999</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>-13.5589046948786</v>
+        <v>11.06094562000001</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>10.90560055084911</v>
       </c>
     </row>
     <row r="11">
@@ -1471,16 +1471,16 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>170.82634104</v>
+        <v>213.48660962</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>212.10658592</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>-41.28024487999996</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>-24.16503487031542</v>
+        <v>1.38002370000002</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.6464216666592917</v>
       </c>
     </row>
     <row r="12">
@@ -1491,16 +1491,16 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>209.89549308</v>
+        <v>207.66048284</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>212.10658592</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>-2.211092839999997</v>
+        <v>-4.446103079999972</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>-1.053425591733529</v>
+        <v>-2.14104437165623</v>
       </c>
     </row>
     <row r="13">
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>56.282888</v>
+        <v>88.71947573999999</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>73.62148692</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>-17.33859892</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>-30.80616424658237</v>
+        <v>15.09798882</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <v>17.01767136704678</v>
       </c>
     </row>
     <row r="24">
@@ -1791,16 +1791,16 @@
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>332.46828218</v>
+        <v>142.65096726</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>388.3581053</v>
+        <v>128.19088714</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>-55.88982312000002</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>-16.81057295256243</v>
+        <v>14.46008012</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>10.13668564451064</v>
       </c>
     </row>
     <row r="27">
@@ -1811,16 +1811,16 @@
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>431.01602148</v>
+        <v>116.82890448</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>388.3581053</v>
+        <v>128.19088714</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>42.65791618</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>9.897060446505796</v>
+        <v>-11.36198266000001</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>-9.725318156984921</v>
       </c>
     </row>
     <row r="28">
@@ -1831,16 +1831,16 @@
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>411.42811356</v>
+        <v>116.82890448</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>388.3581053</v>
+        <v>128.19088714</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>23.07000825999997</v>
-      </c>
-      <c r="F28" s="16" t="n">
-        <v>5.607299914529442</v>
+        <v>-11.36198266000001</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>-9.725318156984921</v>
       </c>
     </row>
     <row r="29">
@@ -1855,16 +1855,16 @@
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>676.8887525199999</v>
+        <v>742.6929709799999</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>710.5593757999999</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>-33.67062328000006</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>-4.974321578641566</v>
+        <v>32.13359518000006</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>4.326632462617637</v>
       </c>
     </row>
     <row r="30">
@@ -1931,16 +1931,16 @@
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>435.079712246</v>
+        <v>426.0262960539999</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>375.154830312</v>
+        <v>291.058400246</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>59.92488193399998</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>-256.2669953544086</v>
+        <v>134.967895808</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>9.344940955438062</v>
       </c>
     </row>
     <row r="35">
@@ -1955,16 +1955,16 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>407.994182748</v>
+        <v>326.874306338</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>375.154830312</v>
+        <v>291.058400246</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>32.83935243599996</v>
+        <v>35.81590609200003</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>7.60942522137919</v>
+        <v>7.33496111830676</v>
       </c>
     </row>
     <row r="36">
@@ -1979,16 +1979,16 @@
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>410.62057798</v>
+        <v>331.0413946800001</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>375.154830312</v>
+        <v>291.058400246</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>35.46574766799995</v>
+        <v>39.98299443400009</v>
       </c>
       <c r="F36" s="16" t="n">
-        <v>9.186777199391399</v>
+        <v>8.909574578439571</v>
       </c>
     </row>
   </sheetData>
@@ -2069,16 +2069,16 @@
         </is>
       </c>
       <c r="C2" s="17" t="n">
-        <v>95.52536000000001</v>
+        <v>97.74202</v>
       </c>
       <c r="D2" s="17" t="n">
-        <v>60.24364000000001</v>
+        <v>98.58438000000001</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>-35.28172</v>
+        <v>0.8423600000000135</v>
       </c>
       <c r="F2" s="19" t="n">
-        <v>-36.93440150343322</v>
+        <v>0.861819716842371</v>
       </c>
     </row>
     <row r="3">
@@ -2089,16 +2089,16 @@
         </is>
       </c>
       <c r="C3" s="17" t="n">
-        <v>76.65346</v>
+        <v>100</v>
       </c>
       <c r="D3" s="17" t="n">
-        <v>60.24364000000001</v>
-      </c>
-      <c r="E3" s="18" t="n">
-        <v>-16.40981999999999</v>
-      </c>
-      <c r="F3" s="19" t="n">
-        <v>-21.40780076985434</v>
+        <v>98.58438000000001</v>
+      </c>
+      <c r="E3" s="20" t="n">
+        <v>-1.41561999999999</v>
+      </c>
+      <c r="F3" s="21" t="n">
+        <v>-1.41561999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2109,16 +2109,16 @@
         </is>
       </c>
       <c r="C4" s="17" t="n">
-        <v>77.84826000000001</v>
+        <v>100</v>
       </c>
       <c r="D4" s="17" t="n">
-        <v>60.24364000000001</v>
-      </c>
-      <c r="E4" s="18" t="n">
-        <v>-17.60462</v>
-      </c>
-      <c r="F4" s="19" t="n">
-        <v>-22.61401860491166</v>
+        <v>98.58438000000001</v>
+      </c>
+      <c r="E4" s="20" t="n">
+        <v>-1.41561999999999</v>
+      </c>
+      <c r="F4" s="21" t="n">
+        <v>-1.41561999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2133,16 +2133,16 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>91.67654</v>
+        <v>99.89196</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>96.2818</v>
-      </c>
-      <c r="E5" s="20" t="n">
-        <v>4.605260000000001</v>
-      </c>
-      <c r="F5" s="21" t="n">
-        <v>5.023378936421468</v>
+        <v>100</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>0.1080400000000026</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0.1081568526636204</v>
       </c>
     </row>
     <row r="6">
@@ -2153,16 +2153,16 @@
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>78.01594</v>
+        <v>100</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>96.2818</v>
-      </c>
-      <c r="E6" s="20" t="n">
-        <v>18.26586</v>
-      </c>
-      <c r="F6" s="21" t="n">
-        <v>23.41298457725435</v>
+        <v>100</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2173,16 +2173,16 @@
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>78.28578</v>
+        <v>100</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>96.2818</v>
-      </c>
-      <c r="E7" s="20" t="n">
-        <v>17.99602</v>
-      </c>
-      <c r="F7" s="21" t="n">
-        <v>22.98759749216269</v>
+        <v>100</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2197,16 +2197,16 @@
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>86.72666</v>
+        <v>98.01527999999999</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>79.21602</v>
+        <v>100</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-7.510639999999995</v>
+        <v>1.98472000000001</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>-8.660128269669322</v>
+        <v>2.024908769326589</v>
       </c>
     </row>
     <row r="9">
@@ -2217,16 +2217,16 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>79.23348000000001</v>
+        <v>100</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>79.21602</v>
+        <v>100</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>-0.01746000000001402</v>
+        <v>0</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>-0.02203613926841787</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2237,16 +2237,16 @@
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>79.29212000000001</v>
+        <v>100</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>79.21602</v>
+        <v>100</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>-0.07610000000001094</v>
+        <v>0</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>-0.09597422795608307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2261,16 +2261,16 @@
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>90.72194</v>
+        <v>91.2577</v>
       </c>
       <c r="D11" s="17" t="n">
         <v>93.32698000000001</v>
       </c>
-      <c r="E11" s="20" t="n">
-        <v>2.605040000000002</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>2.871455350271392</v>
+      <c r="E11" s="18" t="n">
+        <v>2.069280000000006</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>2.267512768785545</v>
       </c>
     </row>
     <row r="12">
@@ -2281,16 +2281,16 @@
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>78.11203999999999</v>
+        <v>78.22596</v>
       </c>
       <c r="D12" s="17" t="n">
         <v>93.32698000000001</v>
       </c>
-      <c r="E12" s="20" t="n">
-        <v>15.21494000000001</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>19.47835442525891</v>
+      <c r="E12" s="18" t="n">
+        <v>15.10102000000001</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>19.30435880876375</v>
       </c>
     </row>
     <row r="13">
@@ -2306,10 +2306,10 @@
       <c r="D13" s="17" t="n">
         <v>93.32698000000001</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="18" t="n">
         <v>15.82106</v>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="F13" s="19" t="n">
         <v>20.41271169995789</v>
       </c>
     </row>
@@ -2330,10 +2330,10 @@
       <c r="D14" s="17" t="n">
         <v>90.048</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="18" t="n">
         <v>3.230980000000002</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="19" t="n">
         <v>3.72159744713652</v>
       </c>
     </row>
@@ -2350,10 +2350,10 @@
       <c r="D15" s="17" t="n">
         <v>90.048</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="18" t="n">
         <v>12.39838</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="F15" s="19" t="n">
         <v>15.96708393421629</v>
       </c>
     </row>
@@ -2370,10 +2370,10 @@
       <c r="D16" s="17" t="n">
         <v>90.048</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="18" t="n">
         <v>12.88545999999999</v>
       </c>
-      <c r="F16" s="21" t="n">
+      <c r="F16" s="19" t="n">
         <v>16.69911332623316</v>
       </c>
     </row>
@@ -2394,10 +2394,10 @@
       <c r="D17" s="17" t="n">
         <v>88.08798</v>
       </c>
-      <c r="E17" s="20" t="n">
+      <c r="E17" s="18" t="n">
         <v>5.635459999999995</v>
       </c>
-      <c r="F17" s="21" t="n">
+      <c r="F17" s="19" t="n">
         <v>6.834794133641998</v>
       </c>
     </row>
@@ -2414,10 +2414,10 @@
       <c r="D18" s="17" t="n">
         <v>88.08798</v>
       </c>
-      <c r="E18" s="20" t="n">
+      <c r="E18" s="18" t="n">
         <v>10.82896</v>
       </c>
-      <c r="F18" s="21" t="n">
+      <c r="F18" s="19" t="n">
         <v>14.01643458589042</v>
       </c>
     </row>
@@ -2434,10 +2434,10 @@
       <c r="D19" s="17" t="n">
         <v>88.08798</v>
       </c>
-      <c r="E19" s="20" t="n">
+      <c r="E19" s="18" t="n">
         <v>11.23626000000002</v>
       </c>
-      <c r="F19" s="21" t="n">
+      <c r="F19" s="19" t="n">
         <v>14.62070074684082</v>
       </c>
     </row>
@@ -2458,10 +2458,10 @@
       <c r="D20" s="17" t="n">
         <v>91.36892</v>
       </c>
-      <c r="E20" s="20" t="n">
+      <c r="E20" s="18" t="n">
         <v>11.16231999999999</v>
       </c>
-      <c r="F20" s="21" t="n">
+      <c r="F20" s="19" t="n">
         <v>13.91695945221465</v>
       </c>
     </row>
@@ -2478,10 +2478,10 @@
       <c r="D21" s="17" t="n">
         <v>91.36892</v>
       </c>
-      <c r="E21" s="20" t="n">
+      <c r="E21" s="18" t="n">
         <v>14.80524</v>
       </c>
-      <c r="F21" s="21" t="n">
+      <c r="F21" s="19" t="n">
         <v>19.33715829751129</v>
       </c>
     </row>
@@ -2498,10 +2498,10 @@
       <c r="D22" s="17" t="n">
         <v>91.36892</v>
       </c>
-      <c r="E22" s="20" t="n">
+      <c r="E22" s="18" t="n">
         <v>15.12442</v>
       </c>
-      <c r="F22" s="21" t="n">
+      <c r="F22" s="19" t="n">
         <v>19.83673576454695</v>
       </c>
     </row>
@@ -2517,16 +2517,16 @@
         </is>
       </c>
       <c r="C23" s="17" t="n">
-        <v>95.48144000000001</v>
+        <v>95.30121999999999</v>
       </c>
       <c r="D23" s="17" t="n">
         <v>93.75758</v>
       </c>
-      <c r="E23" s="18" t="n">
-        <v>-1.723860000000002</v>
-      </c>
-      <c r="F23" s="19" t="n">
-        <v>-1.805439884442466</v>
+      <c r="E23" s="20" t="n">
+        <v>-1.543639999999982</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>-1.619748414553331</v>
       </c>
     </row>
     <row r="24">
@@ -2542,10 +2542,10 @@
       <c r="D24" s="17" t="n">
         <v>93.75758</v>
       </c>
-      <c r="E24" s="20" t="n">
+      <c r="E24" s="18" t="n">
         <v>13.34034</v>
       </c>
-      <c r="F24" s="21" t="n">
+      <c r="F24" s="19" t="n">
         <v>16.58890556303598</v>
       </c>
     </row>
@@ -2562,10 +2562,10 @@
       <c r="D25" s="17" t="n">
         <v>93.75758</v>
       </c>
-      <c r="E25" s="20" t="n">
+      <c r="E25" s="18" t="n">
         <v>13.34034</v>
       </c>
-      <c r="F25" s="21" t="n">
+      <c r="F25" s="19" t="n">
         <v>16.58890556303598</v>
       </c>
     </row>
@@ -2581,16 +2581,16 @@
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>90.82626</v>
+        <v>95.89005999999999</v>
       </c>
       <c r="D26" s="17" t="n">
-        <v>84.27312000000001</v>
+        <v>99.76740000000001</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>-6.553139999999999</v>
+        <v>3.877340000000018</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>-7.21502790052128</v>
+        <v>4.043526513592774</v>
       </c>
     </row>
     <row r="27">
@@ -2601,16 +2601,16 @@
         </is>
       </c>
       <c r="C27" s="17" t="n">
-        <v>77.58844000000001</v>
+        <v>99.33788000000001</v>
       </c>
       <c r="D27" s="17" t="n">
-        <v>84.27312000000001</v>
-      </c>
-      <c r="E27" s="20" t="n">
-        <v>6.68468</v>
-      </c>
-      <c r="F27" s="21" t="n">
-        <v>8.6155618027634</v>
+        <v>99.76740000000001</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>0.4295199999999966</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>0.4323828936152014</v>
       </c>
     </row>
     <row r="28">
@@ -2621,16 +2621,16 @@
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>77.66758000000002</v>
+        <v>99.33788000000001</v>
       </c>
       <c r="D28" s="17" t="n">
-        <v>84.27312000000001</v>
-      </c>
-      <c r="E28" s="20" t="n">
-        <v>6.605539999999991</v>
-      </c>
-      <c r="F28" s="21" t="n">
-        <v>8.504887109911225</v>
+        <v>99.76740000000001</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>0.4295199999999966</v>
+      </c>
+      <c r="F28" s="19" t="n">
+        <v>0.4323828936152014</v>
       </c>
     </row>
     <row r="29">
@@ -2645,16 +2645,16 @@
         </is>
       </c>
       <c r="C29" s="17" t="n">
-        <v>87.71088</v>
+        <v>87.47286000000001</v>
       </c>
       <c r="D29" s="17" t="n">
         <v>94.87696</v>
       </c>
-      <c r="E29" s="20" t="n">
-        <v>7.166079999999994</v>
-      </c>
-      <c r="F29" s="21" t="n">
-        <v>8.170115269622187</v>
+      <c r="E29" s="18" t="n">
+        <v>7.404099999999985</v>
+      </c>
+      <c r="F29" s="19" t="n">
+        <v>8.464454003218808</v>
       </c>
     </row>
     <row r="30">
@@ -2670,10 +2670,10 @@
       <c r="D30" s="17" t="n">
         <v>94.87696</v>
       </c>
-      <c r="E30" s="20" t="n">
+      <c r="E30" s="18" t="n">
         <v>17.25840000000001</v>
       </c>
-      <c r="F30" s="21" t="n">
+      <c r="F30" s="19" t="n">
         <v>22.234888150463</v>
       </c>
     </row>
@@ -2690,10 +2690,10 @@
       <c r="D31" s="17" t="n">
         <v>94.87696</v>
       </c>
-      <c r="E31" s="20" t="n">
+      <c r="E31" s="18" t="n">
         <v>17.37512000000001</v>
       </c>
-      <c r="F31" s="21" t="n">
+      <c r="F31" s="19" t="n">
         <v>22.41897740750415</v>
       </c>
     </row>
@@ -2721,16 +2721,16 @@
         </is>
       </c>
       <c r="C34" s="17" t="n">
-        <v>88.814522</v>
+        <v>91.504724</v>
       </c>
       <c r="D34" s="17" t="n">
-        <v>87.14810000000003</v>
+        <v>94.98182000000001</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>-1.666421999999969</v>
+        <v>3.477096000000017</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-1.407669696875808</v>
+        <v>4.062398124286953</v>
       </c>
     </row>
     <row r="35">
@@ -2745,16 +2745,16 @@
         </is>
       </c>
       <c r="C35" s="17" t="n">
-        <v>77.911148</v>
+        <v>86.70719600000001</v>
       </c>
       <c r="D35" s="17" t="n">
-        <v>87.14810000000003</v>
-      </c>
-      <c r="E35" s="20" t="n">
-        <v>9.236952000000031</v>
-      </c>
-      <c r="F35" s="21" t="n">
-        <v>11.82215344272709</v>
+        <v>94.98182000000001</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>8.274624000000003</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>10.64655922334959</v>
       </c>
     </row>
     <row r="36">
@@ -2769,16 +2769,16 @@
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>77.87775000000001</v>
+        <v>86.50216400000001</v>
       </c>
       <c r="D36" s="17" t="n">
-        <v>87.14810000000003</v>
-      </c>
-      <c r="E36" s="20" t="n">
-        <v>9.270350000000022</v>
-      </c>
-      <c r="F36" s="21" t="n">
-        <v>11.93596362773251</v>
+        <v>94.98182000000001</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>8.479656000000006</v>
+      </c>
+      <c r="F36" s="19" t="n">
+        <v>10.95939074017341</v>
       </c>
     </row>
   </sheetData>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="D2" s="22" t="n">
-        <v>11767.11598</v>
+        <v>55269.7481</v>
       </c>
       <c r="E2" s="22" t="n">
-        <v>4359.31291184611</v>
+        <v>399.9181018196423</v>
       </c>
       <c r="F2" s="22" t="n">
-        <v>6936.6421</v>
+        <v>54955.6124</v>
       </c>
       <c r="G2" s="22" t="n">
-        <v>15573.6263</v>
+        <v>55856.4083</v>
       </c>
       <c r="H2" s="22" t="n">
-        <v>3821.106242383536</v>
+        <v>350.5436719517498</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>5</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="D3" s="22" t="n">
-        <v>95.52536000000001</v>
+        <v>97.74202</v>
       </c>
       <c r="E3" s="22" t="n">
-        <v>0.6405998618482535</v>
+        <v>0.5015624856386327</v>
       </c>
       <c r="F3" s="22" t="n">
-        <v>94.6785</v>
+        <v>97.15649999999999</v>
       </c>
       <c r="G3" s="22" t="n">
-        <v>96.1442</v>
+        <v>98.35890000000001</v>
       </c>
       <c r="H3" s="22" t="n">
-        <v>0.5615105362881101</v>
+        <v>0.4396389026378839</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>5</v>
@@ -2952,19 +2952,19 @@
         </is>
       </c>
       <c r="D4" s="22" t="n">
-        <v>36.8</v>
+        <v>37.2</v>
       </c>
       <c r="E4" s="22" t="n">
-        <v>5.630275304103699</v>
+        <v>8.555699854482976</v>
       </c>
       <c r="F4" s="22" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G4" s="22" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H4" s="22" t="n">
-        <v>4.935153898309554</v>
+        <v>7.499401576125925</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>5</v>
@@ -2987,19 +2987,19 @@
         </is>
       </c>
       <c r="D5" s="22" t="n">
-        <v>308.41652</v>
+        <v>1241.9461</v>
       </c>
       <c r="E5" s="22" t="n">
-        <v>3.898598787641527</v>
+        <v>7.008366933530203</v>
       </c>
       <c r="F5" s="22" t="n">
-        <v>305.328</v>
+        <v>1233.9499</v>
       </c>
       <c r="G5" s="22" t="n">
-        <v>314.8135</v>
+        <v>1252.626</v>
       </c>
       <c r="H5" s="22" t="n">
-        <v>3.41727250721657</v>
+        <v>6.143104470857031</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>5</v>
@@ -3022,19 +3022,19 @@
         </is>
       </c>
       <c r="D6" s="22" t="n">
-        <v>264227.33266</v>
+        <v>65732.06165999999</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>12022.47031019097</v>
+        <v>1054.899613857103</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>251976.9471</v>
+        <v>64657.1259</v>
       </c>
       <c r="G6" s="22" t="n">
-        <v>280502.0414</v>
+        <v>67224.15760000001</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>10538.15986145551</v>
+        <v>924.6602804409224</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>5</v>
@@ -3057,19 +3057,19 @@
         </is>
       </c>
       <c r="D7" s="22" t="n">
-        <v>76.65346</v>
+        <v>100</v>
       </c>
       <c r="E7" s="22" t="n">
-        <v>1.994506478555532</v>
+        <v>0</v>
       </c>
       <c r="F7" s="22" t="n">
-        <v>74.02500000000001</v>
+        <v>100</v>
       </c>
       <c r="G7" s="22" t="n">
-        <v>79.5521</v>
+        <v>100</v>
       </c>
       <c r="H7" s="22" t="n">
-        <v>1.748262010504647</v>
+        <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>5</v>
@@ -3092,19 +3092,19 @@
         </is>
       </c>
       <c r="D8" s="22" t="n">
-        <v>192.6</v>
+        <v>0</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>24.09979253022731</v>
+        <v>0</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="G8" s="22" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>21.12439954176212</v>
+        <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>5</v>
@@ -3127,19 +3127,19 @@
         </is>
       </c>
       <c r="D9" s="22" t="n">
-        <v>532.2492599999999</v>
+        <v>1364.7725</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>5.304271811757019</v>
+        <v>4.788456220954728</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>525.9979</v>
+        <v>1359.8656</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>538.4769</v>
+        <v>1369.9126</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>4.649399238152067</v>
+        <v>4.197266937995918</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>5</v>
@@ -3162,19 +3162,19 @@
         </is>
       </c>
       <c r="D10" s="22" t="n">
-        <v>262185.04354</v>
+        <v>65769.2102</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>11948.03485310827</v>
+        <v>1061.810739992985</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>248989.8342</v>
+        <v>64686.3254</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>280428.6799</v>
+        <v>67275.3553</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>10472.91430660203</v>
+        <v>930.7181495945586</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>5</v>
@@ -3197,19 +3197,19 @@
         </is>
       </c>
       <c r="D11" s="22" t="n">
-        <v>77.84826000000001</v>
+        <v>100</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>2.145666060457688</v>
+        <v>0</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>74.4224</v>
+        <v>100</v>
       </c>
       <c r="G11" s="22" t="n">
-        <v>80.1319</v>
+        <v>100</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>1.880759225933444</v>
+        <v>0</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>5</v>
@@ -3232,19 +3232,19 @@
         </is>
       </c>
       <c r="D12" s="22" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>23.36664289109585</v>
+        <v>0</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>20.48176554889739</v>
+        <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>5</v>
@@ -3267,19 +3267,19 @@
         </is>
       </c>
       <c r="D13" s="22" t="n">
-        <v>532.39698</v>
+        <v>1364.7725</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>4.869274794258377</v>
+        <v>4.788456220954728</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>527.5962</v>
+        <v>1359.8656</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>538.6328</v>
+        <v>1369.9126</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>4.268107540906509</v>
+        <v>4.197266937995918</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>5</v>
@@ -3302,19 +3302,19 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>294123.57576</v>
+        <v>83128.25876</v>
       </c>
       <c r="E14" s="25" t="n">
-        <v>12965.51234741584</v>
+        <v>2780.521259968773</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>281582.3653</v>
+        <v>79519.21000000001</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>315991.7867</v>
+        <v>86003.7251</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>11364.7726529984</v>
+        <v>2437.234343668028</v>
       </c>
       <c r="I14" s="23" t="n">
         <v>5</v>
@@ -3337,19 +3337,19 @@
         </is>
       </c>
       <c r="D15" s="25" t="n">
-        <v>60.24364000000001</v>
+        <v>98.58438000000001</v>
       </c>
       <c r="E15" s="25" t="n">
-        <v>2.389545825674829</v>
+        <v>0.3075080925764394</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>57.4001</v>
+        <v>98.1159</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>63.6452</v>
+        <v>98.92749999999999</v>
       </c>
       <c r="H15" s="25" t="n">
-        <v>2.094529265411434</v>
+        <v>0.269542727463829</v>
       </c>
       <c r="I15" s="23" t="n">
         <v>5</v>
@@ -3372,19 +3372,19 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>189.6</v>
+        <v>0</v>
       </c>
       <c r="E16" s="25" t="n">
-        <v>24.85558287387363</v>
+        <v>0</v>
       </c>
       <c r="F16" s="25" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G16" s="25" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="H16" s="25" t="n">
-        <v>21.78687898713352</v>
+        <v>0</v>
       </c>
       <c r="I16" s="23" t="n">
         <v>5</v>
@@ -3407,19 +3407,19 @@
         </is>
       </c>
       <c r="D17" s="25" t="n">
-        <v>524.28688</v>
+        <v>1363.14264</v>
       </c>
       <c r="E17" s="25" t="n">
-        <v>5.967543536246716</v>
+        <v>4.577684814728939</v>
       </c>
       <c r="F17" s="25" t="n">
-        <v>516.0865</v>
+        <v>1357.3215</v>
       </c>
       <c r="G17" s="25" t="n">
-        <v>530.8414</v>
+        <v>1367.7311</v>
       </c>
       <c r="H17" s="25" t="n">
-        <v>5.230782538248957</v>
+        <v>4.012517654718556</v>
       </c>
       <c r="I17" s="23" t="n">
         <v>5</v>
@@ -3442,19 +3442,19 @@
         </is>
       </c>
       <c r="D18" s="22" t="n">
-        <v>71590.54244</v>
+        <v>73949.04883999999</v>
       </c>
       <c r="E18" s="22" t="n">
-        <v>8762.430134742581</v>
+        <v>734.3443191900858</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>62526.9851</v>
+        <v>73134.618</v>
       </c>
       <c r="G18" s="22" t="n">
-        <v>85621.4614</v>
+        <v>74600.15700000001</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>7680.608656315804</v>
+        <v>643.6811761071353</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>5</v>
@@ -3477,19 +3477,19 @@
         </is>
       </c>
       <c r="D19" s="22" t="n">
-        <v>91.67654</v>
+        <v>99.89196</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>0.973473637547525</v>
+        <v>0.08852543702236282</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>90.50749999999999</v>
+        <v>99.80249999999999</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>92.50660000000001</v>
+        <v>100</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>0.8532872653212209</v>
+        <v>0.07759596680859289</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>5</v>
@@ -3512,19 +3512,19 @@
         </is>
       </c>
       <c r="D20" s="22" t="n">
-        <v>96.40000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>9.09945053286186</v>
+        <v>1.788854381999832</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>109</v>
+        <v>4</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>7.976020060155316</v>
+        <v>1.568</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>5</v>
@@ -3547,19 +3547,19 @@
         </is>
       </c>
       <c r="D21" s="22" t="n">
-        <v>127.63524</v>
+        <v>1086.84812</v>
       </c>
       <c r="E21" s="22" t="n">
-        <v>2.519026134838627</v>
+        <v>6.662216811392407</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>124.4403</v>
+        <v>1079.0749</v>
       </c>
       <c r="G21" s="22" t="n">
-        <v>131.0979</v>
+        <v>1092.7467</v>
       </c>
       <c r="H21" s="22" t="n">
-        <v>2.208023760442307</v>
+        <v>5.839690511077204</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>5</v>
@@ -3582,19 +3582,19 @@
         </is>
       </c>
       <c r="D22" s="22" t="n">
-        <v>105435.04684</v>
+        <v>71549.82554000001</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>5233.6398032816</v>
+        <v>235.7054305501574</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>96975.68060000001</v>
+        <v>71222.51609999999</v>
       </c>
       <c r="G22" s="22" t="n">
-        <v>110531.9235</v>
+        <v>71887.71060000001</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>4587.487552995423</v>
+        <v>206.604919227395</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>5</v>
@@ -3617,19 +3617,19 @@
         </is>
       </c>
       <c r="D23" s="22" t="n">
-        <v>78.01594</v>
+        <v>100</v>
       </c>
       <c r="E23" s="22" t="n">
-        <v>0.7242246150194036</v>
+        <v>0</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>77.2227</v>
+        <v>100</v>
       </c>
       <c r="G23" s="22" t="n">
-        <v>79.17230000000001</v>
+        <v>100</v>
       </c>
       <c r="H23" s="22" t="n">
-        <v>0.6348108643035046</v>
+        <v>0</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>5</v>
@@ -3652,19 +3652,19 @@
         </is>
       </c>
       <c r="D24" s="22" t="n">
-        <v>360.2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="22" t="n">
-        <v>16.08415369237686</v>
+        <v>0</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="G24" s="22" t="n">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>14.09838231854988</v>
+        <v>0</v>
       </c>
       <c r="I24" s="5" t="n">
         <v>5</v>
@@ -3687,19 +3687,19 @@
         </is>
       </c>
       <c r="D25" s="22" t="n">
-        <v>137.48416</v>
+        <v>1118.05842</v>
       </c>
       <c r="E25" s="22" t="n">
-        <v>1.696359159494238</v>
+        <v>4.455820203060282</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>135.5447</v>
+        <v>1112.2753</v>
       </c>
       <c r="G25" s="22" t="n">
-        <v>138.9913</v>
+        <v>1124.7298</v>
       </c>
       <c r="H25" s="22" t="n">
-        <v>1.486924362794342</v>
+        <v>3.905698612867404</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>5</v>
@@ -3722,19 +3722,19 @@
         </is>
       </c>
       <c r="D26" s="22" t="n">
-        <v>109947.82728</v>
+        <v>71549.82554000001</v>
       </c>
       <c r="E26" s="22" t="n">
-        <v>8589.009833161967</v>
+        <v>235.7054305501574</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>102136.3529</v>
+        <v>71222.51609999999</v>
       </c>
       <c r="G26" s="22" t="n">
-        <v>120436.4608</v>
+        <v>71887.71060000001</v>
       </c>
       <c r="H26" s="22" t="n">
-        <v>7528.599059774799</v>
+        <v>206.604919227395</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>5</v>
@@ -3757,19 +3757,19 @@
         </is>
       </c>
       <c r="D27" s="22" t="n">
-        <v>78.28578</v>
+        <v>100</v>
       </c>
       <c r="E27" s="22" t="n">
-        <v>0.8055488731293681</v>
+        <v>0</v>
       </c>
       <c r="F27" s="22" t="n">
-        <v>76.91930000000001</v>
+        <v>100</v>
       </c>
       <c r="G27" s="22" t="n">
-        <v>78.9027</v>
+        <v>100</v>
       </c>
       <c r="H27" s="22" t="n">
-        <v>0.7060947194901233</v>
+        <v>0</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>5</v>
@@ -3792,19 +3792,19 @@
         </is>
       </c>
       <c r="D28" s="22" t="n">
-        <v>355.4</v>
+        <v>0</v>
       </c>
       <c r="E28" s="22" t="n">
-        <v>15.94678651014053</v>
+        <v>0</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="G28" s="22" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>13.97797467446554</v>
+        <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>5</v>
@@ -3827,19 +3827,19 @@
         </is>
       </c>
       <c r="D29" s="22" t="n">
-        <v>138.90948</v>
+        <v>1118.05842</v>
       </c>
       <c r="E29" s="22" t="n">
-        <v>1.793772565572341</v>
+        <v>4.455820203060282</v>
       </c>
       <c r="F29" s="22" t="n">
-        <v>137.0769</v>
+        <v>1112.2753</v>
       </c>
       <c r="G29" s="22" t="n">
-        <v>141.2462</v>
+        <v>1124.7298</v>
       </c>
       <c r="H29" s="22" t="n">
-        <v>1.572310977975229</v>
+        <v>3.905698612867404</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>5</v>
@@ -3862,19 +3862,19 @@
         </is>
       </c>
       <c r="D30" s="25" t="n">
-        <v>116941.21104</v>
+        <v>74449.27092000001</v>
       </c>
       <c r="E30" s="25" t="n">
-        <v>6838.034393597838</v>
+        <v>371.6350580504185</v>
       </c>
       <c r="F30" s="25" t="n">
-        <v>105311.0254</v>
+        <v>74091.1056</v>
       </c>
       <c r="G30" s="25" t="n">
-        <v>122048.4074</v>
+        <v>74854.28350000001</v>
       </c>
       <c r="H30" s="25" t="n">
-        <v>5993.801416733996</v>
+        <v>325.752491028144</v>
       </c>
       <c r="I30" s="23" t="n">
         <v>5</v>
@@ -3897,19 +3897,19 @@
         </is>
       </c>
       <c r="D31" s="25" t="n">
-        <v>96.2818</v>
+        <v>100</v>
       </c>
       <c r="E31" s="25" t="n">
-        <v>1.145327715110394</v>
+        <v>0</v>
       </c>
       <c r="F31" s="25" t="n">
-        <v>94.75360000000001</v>
+        <v>100</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>97.9182</v>
+        <v>100</v>
       </c>
       <c r="H31" s="25" t="n">
-        <v>1.00392400598053</v>
+        <v>0</v>
       </c>
       <c r="I31" s="23" t="n">
         <v>5</v>
@@ -3932,19 +3932,19 @@
         </is>
       </c>
       <c r="D32" s="25" t="n">
-        <v>27.8</v>
+        <v>0</v>
       </c>
       <c r="E32" s="25" t="n">
-        <v>18.72698587600258</v>
+        <v>0</v>
       </c>
       <c r="F32" s="25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G32" s="25" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H32" s="25" t="n">
-        <v>16.41492686550873</v>
+        <v>0</v>
       </c>
       <c r="I32" s="23" t="n">
         <v>5</v>
@@ -3967,19 +3967,19 @@
         </is>
       </c>
       <c r="D33" s="25" t="n">
-        <v>174.29036</v>
+        <v>1116.70774</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>8.190445767050784</v>
+        <v>4.434094124282868</v>
       </c>
       <c r="F33" s="25" t="n">
-        <v>162.5245</v>
+        <v>1110.9595</v>
       </c>
       <c r="G33" s="25" t="n">
-        <v>185.6364</v>
+        <v>1123.3581</v>
       </c>
       <c r="H33" s="25" t="n">
-        <v>7.179242252451175</v>
+        <v>3.886654865167327</v>
       </c>
       <c r="I33" s="23" t="n">
         <v>5</v>
@@ -4002,19 +4002,19 @@
         </is>
       </c>
       <c r="D34" s="22" t="n">
-        <v>174952.73972</v>
+        <v>87473.67942</v>
       </c>
       <c r="E34" s="22" t="n">
-        <v>36719.72099765508</v>
+        <v>956.4490000617426</v>
       </c>
       <c r="F34" s="22" t="n">
-        <v>138003.4301</v>
+        <v>86478.21520000001</v>
       </c>
       <c r="G34" s="22" t="n">
-        <v>221332.851</v>
+        <v>88934.33319999999</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>32186.25456810859</v>
+        <v>838.3645126107048</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>5</v>
@@ -4037,19 +4037,19 @@
         </is>
       </c>
       <c r="D35" s="22" t="n">
-        <v>86.72666</v>
+        <v>98.01527999999999</v>
       </c>
       <c r="E35" s="22" t="n">
-        <v>2.144783228673703</v>
+        <v>0.3791459244143317</v>
       </c>
       <c r="F35" s="22" t="n">
-        <v>83.4426</v>
+        <v>97.4089</v>
       </c>
       <c r="G35" s="22" t="n">
-        <v>88.53</v>
+        <v>98.3817</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>1.879985389755824</v>
+        <v>0.3323360556699176</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>5</v>
@@ -4072,19 +4072,19 @@
         </is>
       </c>
       <c r="D36" s="22" t="n">
-        <v>202.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E36" s="22" t="n">
-        <v>33.67046183229449</v>
+        <v>13.44618905117729</v>
       </c>
       <c r="F36" s="22" t="n">
-        <v>168</v>
+        <v>57</v>
       </c>
       <c r="G36" s="22" t="n">
-        <v>254</v>
+        <v>91</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>29.51346106440246</v>
+        <v>11.78610436064436</v>
       </c>
       <c r="I36" s="5" t="n">
         <v>5</v>
@@ -4107,19 +4107,19 @@
         </is>
       </c>
       <c r="D37" s="22" t="n">
-        <v>102.63728</v>
+        <v>787.1169199999999</v>
       </c>
       <c r="E37" s="22" t="n">
-        <v>7.502537281613471</v>
+        <v>4.690513802559372</v>
       </c>
       <c r="F37" s="22" t="n">
-        <v>94.2833</v>
+        <v>780.9278</v>
       </c>
       <c r="G37" s="22" t="n">
-        <v>114.3293</v>
+        <v>790.9648</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>6.576263879242367</v>
+        <v>4.111416623074122</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>5</v>
@@ -4142,19 +4142,19 @@
         </is>
       </c>
       <c r="D38" s="22" t="n">
-        <v>364807.10478</v>
+        <v>102410.96022</v>
       </c>
       <c r="E38" s="22" t="n">
-        <v>10899.90210067903</v>
+        <v>3207.500252482648</v>
       </c>
       <c r="F38" s="22" t="n">
-        <v>348535.4485</v>
+        <v>97558.2885</v>
       </c>
       <c r="G38" s="22" t="n">
-        <v>377078.6918</v>
+        <v>106449.1803</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>9554.185441722739</v>
+        <v>2811.497932140384</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>5</v>
@@ -4177,19 +4177,19 @@
         </is>
       </c>
       <c r="D39" s="22" t="n">
-        <v>79.23348000000001</v>
+        <v>100</v>
       </c>
       <c r="E39" s="22" t="n">
-        <v>0.9273289637447975</v>
+        <v>0</v>
       </c>
       <c r="F39" s="22" t="n">
-        <v>77.6995</v>
+        <v>100</v>
       </c>
       <c r="G39" s="22" t="n">
-        <v>80.05119999999999</v>
+        <v>100</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>0.8128396753716195</v>
+        <v>0</v>
       </c>
       <c r="I39" s="5" t="n">
         <v>5</v>
@@ -4212,19 +4212,19 @@
         </is>
       </c>
       <c r="D40" s="22" t="n">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>22.29349680960796</v>
+        <v>0</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>451</v>
+        <v>0</v>
       </c>
       <c r="G40" s="22" t="n">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>19.54111153440356</v>
+        <v>0</v>
       </c>
       <c r="I40" s="5" t="n">
         <v>5</v>
@@ -4247,19 +4247,19 @@
         </is>
       </c>
       <c r="D41" s="22" t="n">
-        <v>239.3373</v>
+        <v>868.50954</v>
       </c>
       <c r="E41" s="22" t="n">
-        <v>2.110330272729831</v>
+        <v>2.464000302962649</v>
       </c>
       <c r="F41" s="22" t="n">
-        <v>236.5355</v>
+        <v>866.0083</v>
       </c>
       <c r="G41" s="22" t="n">
-        <v>242.0356</v>
+        <v>872.0253</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>1.849786042361433</v>
+        <v>2.159791492209787</v>
       </c>
       <c r="I41" s="5" t="n">
         <v>5</v>
@@ -4282,19 +4282,19 @@
         </is>
       </c>
       <c r="D42" s="22" t="n">
-        <v>367803.24106</v>
+        <v>101424.45222</v>
       </c>
       <c r="E42" s="22" t="n">
-        <v>9269.281261966093</v>
+        <v>4178.583039550239</v>
       </c>
       <c r="F42" s="22" t="n">
-        <v>351724.9921</v>
+        <v>96861.76489999999</v>
       </c>
       <c r="G42" s="22" t="n">
-        <v>374573.0088</v>
+        <v>107480.9504</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>8124.883257693918</v>
+        <v>3662.689524616314</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>5</v>
@@ -4317,19 +4317,19 @@
         </is>
       </c>
       <c r="D43" s="22" t="n">
-        <v>79.29212000000001</v>
+        <v>100</v>
       </c>
       <c r="E43" s="22" t="n">
-        <v>0.862403050783098</v>
+        <v>0</v>
       </c>
       <c r="F43" s="22" t="n">
-        <v>78.06870000000001</v>
+        <v>100</v>
       </c>
       <c r="G43" s="22" t="n">
-        <v>80.3947</v>
+        <v>100</v>
       </c>
       <c r="H43" s="22" t="n">
-        <v>0.7559296034572504</v>
+        <v>0</v>
       </c>
       <c r="I43" s="5" t="n">
         <v>5</v>
@@ -4352,19 +4352,19 @@
         </is>
       </c>
       <c r="D44" s="22" t="n">
-        <v>468.4</v>
+        <v>0</v>
       </c>
       <c r="E44" s="22" t="n">
-        <v>21.84719661649979</v>
+        <v>0</v>
       </c>
       <c r="F44" s="22" t="n">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="G44" s="22" t="n">
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>19.1499121669004</v>
+        <v>0</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>5</v>
@@ -4387,19 +4387,19 @@
         </is>
       </c>
       <c r="D45" s="22" t="n">
-        <v>239.49054</v>
+        <v>867.96276</v>
       </c>
       <c r="E45" s="22" t="n">
-        <v>3.557932111915568</v>
+        <v>1.619073112308416</v>
       </c>
       <c r="F45" s="22" t="n">
-        <v>235.2359</v>
+        <v>866.0083</v>
       </c>
       <c r="G45" s="22" t="n">
-        <v>243.7779</v>
+        <v>869.8886</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>3.118665000136459</v>
+        <v>1.419180155548197</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>5</v>
@@ -4422,19 +4422,19 @@
         </is>
       </c>
       <c r="D46" s="25" t="n">
-        <v>417673.33198</v>
+        <v>90363.50659999999</v>
       </c>
       <c r="E46" s="25" t="n">
-        <v>16830.67770439619</v>
+        <v>442.3430938406009</v>
       </c>
       <c r="F46" s="25" t="n">
-        <v>400036.4539</v>
+        <v>89742.3722</v>
       </c>
       <c r="G46" s="25" t="n">
-        <v>440124.7085</v>
+        <v>90851.30809999999</v>
       </c>
       <c r="H46" s="25" t="n">
-        <v>14752.73946613264</v>
+        <v>387.7308170644197</v>
       </c>
       <c r="I46" s="23" t="n">
         <v>5</v>
@@ -4457,19 +4457,19 @@
         </is>
       </c>
       <c r="D47" s="25" t="n">
-        <v>79.21602</v>
+        <v>100</v>
       </c>
       <c r="E47" s="25" t="n">
-        <v>2.957726197098033</v>
+        <v>0</v>
       </c>
       <c r="F47" s="25" t="n">
-        <v>76.1135</v>
+        <v>100</v>
       </c>
       <c r="G47" s="25" t="n">
-        <v>83.55459999999999</v>
+        <v>100</v>
       </c>
       <c r="H47" s="25" t="n">
-        <v>2.592561319532912</v>
+        <v>0</v>
       </c>
       <c r="I47" s="23" t="n">
         <v>5</v>
@@ -4492,19 +4492,19 @@
         </is>
       </c>
       <c r="D48" s="25" t="n">
-        <v>316.8</v>
+        <v>0</v>
       </c>
       <c r="E48" s="25" t="n">
-        <v>58.64042973921661</v>
+        <v>0</v>
       </c>
       <c r="F48" s="25" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="G48" s="25" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="H48" s="25" t="n">
-        <v>51.40060295366192</v>
+        <v>0</v>
       </c>
       <c r="I48" s="23" t="n">
         <v>5</v>
@@ -4527,19 +4527,19 @@
         </is>
       </c>
       <c r="D49" s="25" t="n">
-        <v>238.41418</v>
+        <v>869.8110199999999</v>
       </c>
       <c r="E49" s="25" t="n">
-        <v>2.382390594969681</v>
+        <v>3.779805174476605</v>
       </c>
       <c r="F49" s="25" t="n">
-        <v>236.2877</v>
+        <v>866.2306</v>
       </c>
       <c r="G49" s="25" t="n">
-        <v>242.4862</v>
+        <v>875.2281</v>
       </c>
       <c r="H49" s="25" t="n">
-        <v>2.088257429168883</v>
+        <v>3.313145314239375</v>
       </c>
       <c r="I49" s="23" t="n">
         <v>5</v>
@@ -4562,19 +4562,19 @@
         </is>
       </c>
       <c r="D50" s="22" t="n">
-        <v>170826.34104</v>
+        <v>213486.60962</v>
       </c>
       <c r="E50" s="22" t="n">
-        <v>20353.0668060659</v>
+        <v>27612.57595015751</v>
       </c>
       <c r="F50" s="22" t="n">
-        <v>140353.8038</v>
+        <v>176355.9413</v>
       </c>
       <c r="G50" s="22" t="n">
-        <v>193703.9473</v>
+        <v>242821.6799</v>
       </c>
       <c r="H50" s="22" t="n">
-        <v>17840.24964415149</v>
+        <v>24203.48996850379</v>
       </c>
       <c r="I50" s="5" t="n">
         <v>5</v>
@@ -4597,19 +4597,19 @@
         </is>
       </c>
       <c r="D51" s="22" t="n">
-        <v>90.72194</v>
+        <v>91.2577</v>
       </c>
       <c r="E51" s="22" t="n">
-        <v>1.097952712096472</v>
+        <v>1.122511768312471</v>
       </c>
       <c r="F51" s="22" t="n">
-        <v>89.8002</v>
+        <v>90.28360000000001</v>
       </c>
       <c r="G51" s="22" t="n">
-        <v>92.6118</v>
+        <v>93.0448</v>
       </c>
       <c r="H51" s="22" t="n">
-        <v>0.9623979849285629</v>
+        <v>0.9839249468401505</v>
       </c>
       <c r="I51" s="5" t="n">
         <v>5</v>
@@ -4632,19 +4632,19 @@
         </is>
       </c>
       <c r="D52" s="22" t="n">
-        <v>222.6</v>
+        <v>268.4</v>
       </c>
       <c r="E52" s="22" t="n">
-        <v>24.11016383187804</v>
+        <v>30.21258016125071</v>
       </c>
       <c r="F52" s="22" t="n">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="G52" s="22" t="n">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="H52" s="22" t="n">
-        <v>21.13349038848055</v>
+        <v>26.48249414235751</v>
       </c>
       <c r="I52" s="5" t="n">
         <v>5</v>
@@ -4667,19 +4667,19 @@
         </is>
       </c>
       <c r="D53" s="22" t="n">
-        <v>120.93694</v>
+        <v>107.14572</v>
       </c>
       <c r="E53" s="22" t="n">
-        <v>3.364758347638063</v>
+        <v>1.729021157186925</v>
       </c>
       <c r="F53" s="22" t="n">
-        <v>116.442</v>
+        <v>104.7319</v>
       </c>
       <c r="G53" s="22" t="n">
-        <v>124.9363</v>
+        <v>109.5747</v>
       </c>
       <c r="H53" s="22" t="n">
-        <v>2.949340730126002</v>
+        <v>1.515553866066083</v>
       </c>
       <c r="I53" s="5" t="n">
         <v>5</v>
@@ -4702,19 +4702,19 @@
         </is>
       </c>
       <c r="D54" s="22" t="n">
-        <v>209895.49308</v>
+        <v>207660.48284</v>
       </c>
       <c r="E54" s="22" t="n">
-        <v>14444.0976914024</v>
+        <v>13421.03730013885</v>
       </c>
       <c r="F54" s="22" t="n">
-        <v>196070.6267</v>
+        <v>196040.426</v>
       </c>
       <c r="G54" s="22" t="n">
-        <v>229789.9753</v>
+        <v>229867.5525</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>12660.80985015643</v>
+        <v>11764.05787881492</v>
       </c>
       <c r="I54" s="5" t="n">
         <v>5</v>
@@ -4737,19 +4737,19 @@
         </is>
       </c>
       <c r="D55" s="22" t="n">
-        <v>78.11203999999999</v>
+        <v>78.22596</v>
       </c>
       <c r="E55" s="22" t="n">
-        <v>0.8165520546786948</v>
+        <v>0.6677579973313682</v>
       </c>
       <c r="F55" s="22" t="n">
-        <v>77.1135</v>
+        <v>77.6019</v>
       </c>
       <c r="G55" s="22" t="n">
         <v>79.2418</v>
       </c>
       <c r="H55" s="22" t="n">
-        <v>0.7157394333600453</v>
+        <v>0.5853156916244084</v>
       </c>
       <c r="I55" s="5" t="n">
         <v>5</v>
@@ -4772,19 +4772,19 @@
         </is>
       </c>
       <c r="D56" s="22" t="n">
-        <v>762.4</v>
+        <v>758.8</v>
       </c>
       <c r="E56" s="22" t="n">
-        <v>32.05152102475014</v>
+        <v>28.10160137785745</v>
       </c>
       <c r="F56" s="22" t="n">
         <v>715</v>
       </c>
       <c r="G56" s="22" t="n">
-        <v>797</v>
+        <v>788</v>
       </c>
       <c r="H56" s="22" t="n">
-        <v>28.09439687909317</v>
+        <v>24.63213965533648</v>
       </c>
       <c r="I56" s="5" t="n">
         <v>5</v>
@@ -4807,19 +4807,19 @@
         </is>
       </c>
       <c r="D57" s="22" t="n">
-        <v>118.15874</v>
+        <v>118.1175</v>
       </c>
       <c r="E57" s="22" t="n">
-        <v>1.640536813972791</v>
+        <v>1.688294513703104</v>
       </c>
       <c r="F57" s="22" t="n">
-        <v>116.3656</v>
+        <v>116.3522</v>
       </c>
       <c r="G57" s="22" t="n">
-        <v>120.0553</v>
+        <v>120.0539</v>
       </c>
       <c r="H57" s="22" t="n">
-        <v>1.437993919568562</v>
+        <v>1.479855389082596</v>
       </c>
       <c r="I57" s="5" t="n">
         <v>5</v>
@@ -6802,19 +6802,19 @@
         </is>
       </c>
       <c r="D114" s="22" t="n">
-        <v>56282.888</v>
+        <v>88719.47573999999</v>
       </c>
       <c r="E114" s="22" t="n">
-        <v>5708.317130121548</v>
+        <v>12087.3020614373</v>
       </c>
       <c r="F114" s="22" t="n">
-        <v>49694.5595</v>
+        <v>75904.46309999999</v>
       </c>
       <c r="G114" s="22" t="n">
-        <v>61850.6107</v>
+        <v>107924.222</v>
       </c>
       <c r="H114" s="22" t="n">
-        <v>5003.560574910691</v>
+        <v>10594.98739698728</v>
       </c>
       <c r="I114" s="5" t="n">
         <v>5</v>
@@ -6837,19 +6837,19 @@
         </is>
       </c>
       <c r="D115" s="22" t="n">
-        <v>95.48144000000001</v>
+        <v>95.30121999999999</v>
       </c>
       <c r="E115" s="22" t="n">
-        <v>0.1586560210014107</v>
+        <v>0.4157767093044063</v>
       </c>
       <c r="F115" s="22" t="n">
-        <v>95.3229</v>
+        <v>94.7341</v>
       </c>
       <c r="G115" s="22" t="n">
-        <v>95.6919</v>
+        <v>95.7775</v>
       </c>
       <c r="H115" s="22" t="n">
-        <v>0.1390681340155251</v>
+        <v>0.3644443543026021</v>
       </c>
       <c r="I115" s="5" t="n">
         <v>5</v>
@@ -6872,19 +6872,19 @@
         </is>
       </c>
       <c r="D116" s="22" t="n">
-        <v>176</v>
+        <v>200.4</v>
       </c>
       <c r="E116" s="22" t="n">
-        <v>4.636809247747852</v>
+        <v>15.10959959760681</v>
       </c>
       <c r="F116" s="22" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="G116" s="22" t="n">
-        <v>180</v>
+        <v>216</v>
       </c>
       <c r="H116" s="22" t="n">
-        <v>4.064342505252233</v>
+        <v>13.2441479907165</v>
       </c>
       <c r="I116" s="5" t="n">
         <v>5</v>
@@ -6907,19 +6907,19 @@
         </is>
       </c>
       <c r="D117" s="22" t="n">
-        <v>247.5324</v>
+        <v>234.27062</v>
       </c>
       <c r="E117" s="22" t="n">
-        <v>2.312805728979411</v>
+        <v>3.291988173125775</v>
       </c>
       <c r="F117" s="22" t="n">
-        <v>243.8392</v>
+        <v>230.1917</v>
       </c>
       <c r="G117" s="22" t="n">
-        <v>249.44</v>
+        <v>237.3472</v>
       </c>
       <c r="H117" s="22" t="n">
-        <v>2.027263604869576</v>
+        <v>2.885554859803955</v>
       </c>
       <c r="I117" s="5" t="n">
         <v>5</v>
@@ -7362,19 +7362,19 @@
         </is>
       </c>
       <c r="D130" s="22" t="n">
-        <v>332468.28218</v>
+        <v>142650.96726</v>
       </c>
       <c r="E130" s="22" t="n">
-        <v>15158.5398903619</v>
+        <v>15690.57718531251</v>
       </c>
       <c r="F130" s="22" t="n">
-        <v>312687.7597</v>
+        <v>130513.2153</v>
       </c>
       <c r="G130" s="22" t="n">
-        <v>354370.8627</v>
+        <v>164769.9105</v>
       </c>
       <c r="H130" s="22" t="n">
-        <v>13287.04604872063</v>
+        <v>13753.3972994859</v>
       </c>
       <c r="I130" s="5" t="n">
         <v>5</v>
@@ -7397,19 +7397,19 @@
         </is>
       </c>
       <c r="D131" s="22" t="n">
-        <v>90.82626</v>
+        <v>95.89005999999999</v>
       </c>
       <c r="E131" s="22" t="n">
-        <v>0.5208726888597619</v>
+        <v>0.4296120086775985</v>
       </c>
       <c r="F131" s="22" t="n">
-        <v>90.337</v>
+        <v>95.318</v>
       </c>
       <c r="G131" s="22" t="n">
-        <v>91.527</v>
+        <v>96.3986</v>
       </c>
       <c r="H131" s="22" t="n">
-        <v>0.4565650420461018</v>
+        <v>0.3765715288985092</v>
       </c>
       <c r="I131" s="5" t="n">
         <v>5</v>
@@ -7432,19 +7432,19 @@
         </is>
       </c>
       <c r="D132" s="22" t="n">
-        <v>445.2</v>
+        <v>352.2</v>
       </c>
       <c r="E132" s="22" t="n">
-        <v>14.23727502017152</v>
+        <v>23.91024884855864</v>
       </c>
       <c r="F132" s="22" t="n">
-        <v>432</v>
+        <v>319</v>
       </c>
       <c r="G132" s="22" t="n">
-        <v>463</v>
+        <v>377</v>
       </c>
       <c r="H132" s="22" t="n">
-        <v>12.47952178570958</v>
+        <v>20.95825717945078</v>
       </c>
       <c r="I132" s="5" t="n">
         <v>5</v>
@@ -7467,19 +7467,19 @@
         </is>
       </c>
       <c r="D133" s="22" t="n">
-        <v>119.78742</v>
+        <v>355.7815200000001</v>
       </c>
       <c r="E133" s="22" t="n">
-        <v>2.980630493201058</v>
+        <v>1.158526107603976</v>
       </c>
       <c r="F133" s="22" t="n">
-        <v>117.2202</v>
+        <v>354.4201</v>
       </c>
       <c r="G133" s="22" t="n">
-        <v>123.9024</v>
+        <v>357.5219</v>
       </c>
       <c r="H133" s="22" t="n">
-        <v>2.612637820253666</v>
+        <v>1.015492907081804</v>
       </c>
       <c r="I133" s="5" t="n">
         <v>5</v>
@@ -7502,19 +7502,19 @@
         </is>
       </c>
       <c r="D134" s="22" t="n">
-        <v>431016.02148</v>
+        <v>116828.90448</v>
       </c>
       <c r="E134" s="22" t="n">
-        <v>14388.30877945258</v>
+        <v>578.6024165198683</v>
       </c>
       <c r="F134" s="22" t="n">
-        <v>417050.5175</v>
+        <v>116351.7926</v>
       </c>
       <c r="G134" s="22" t="n">
-        <v>454202.4892</v>
+        <v>117781.2529</v>
       </c>
       <c r="H134" s="22" t="n">
-        <v>12611.9087127483</v>
+        <v>507.1673794313565</v>
       </c>
       <c r="I134" s="5" t="n">
         <v>5</v>
@@ -7537,19 +7537,19 @@
         </is>
       </c>
       <c r="D135" s="22" t="n">
-        <v>77.58844000000001</v>
+        <v>99.33788000000001</v>
       </c>
       <c r="E135" s="22" t="n">
-        <v>0.2878170999089561</v>
+        <v>0.2596339192016336</v>
       </c>
       <c r="F135" s="22" t="n">
-        <v>77.2212</v>
+        <v>99.0368</v>
       </c>
       <c r="G135" s="22" t="n">
-        <v>78.00790000000001</v>
+        <v>99.7106</v>
       </c>
       <c r="H135" s="22" t="n">
-        <v>0.2522828113894435</v>
+        <v>0.2275791642990199</v>
       </c>
       <c r="I135" s="5" t="n">
         <v>5</v>
@@ -7572,19 +7572,19 @@
         </is>
       </c>
       <c r="D136" s="22" t="n">
-        <v>1561.2</v>
+        <v>47</v>
       </c>
       <c r="E136" s="22" t="n">
-        <v>31.40382142351469</v>
+        <v>18.09696107085386</v>
       </c>
       <c r="F136" s="22" t="n">
-        <v>1511</v>
+        <v>21</v>
       </c>
       <c r="G136" s="22" t="n">
-        <v>1594</v>
+        <v>68</v>
       </c>
       <c r="H136" s="22" t="n">
-        <v>27.52666314684727</v>
+        <v>15.86268577511387</v>
       </c>
       <c r="I136" s="5" t="n">
         <v>5</v>
@@ -7607,19 +7607,19 @@
         </is>
       </c>
       <c r="D137" s="22" t="n">
-        <v>124.10894</v>
+        <v>406.45908</v>
       </c>
       <c r="E137" s="22" t="n">
-        <v>0.8280412477648696</v>
+        <v>1.31155783593406</v>
       </c>
       <c r="F137" s="22" t="n">
-        <v>122.7897</v>
+        <v>405.5334</v>
       </c>
       <c r="G137" s="22" t="n">
-        <v>124.8544</v>
+        <v>408.7379</v>
       </c>
       <c r="H137" s="22" t="n">
-        <v>0.7258101551249897</v>
+        <v>1.149631131207861</v>
       </c>
       <c r="I137" s="5" t="n">
         <v>5</v>
@@ -7642,19 +7642,19 @@
         </is>
       </c>
       <c r="D138" s="22" t="n">
-        <v>411428.11356</v>
+        <v>116828.90448</v>
       </c>
       <c r="E138" s="22" t="n">
-        <v>16949.60184162819</v>
+        <v>578.6024165198683</v>
       </c>
       <c r="F138" s="22" t="n">
-        <v>393598.7179</v>
+        <v>116351.7926</v>
       </c>
       <c r="G138" s="22" t="n">
-        <v>432993.4564</v>
+        <v>117781.2529</v>
       </c>
       <c r="H138" s="22" t="n">
-        <v>14856.98106849901</v>
+        <v>507.1673794313565</v>
       </c>
       <c r="I138" s="5" t="n">
         <v>5</v>
@@ -7677,19 +7677,19 @@
         </is>
       </c>
       <c r="D139" s="22" t="n">
-        <v>77.66758000000002</v>
+        <v>99.33788000000001</v>
       </c>
       <c r="E139" s="22" t="n">
-        <v>0.1742303991845273</v>
+        <v>0.2596339192016336</v>
       </c>
       <c r="F139" s="22" t="n">
-        <v>77.488</v>
+        <v>99.0368</v>
       </c>
       <c r="G139" s="22" t="n">
-        <v>77.9152</v>
+        <v>99.7106</v>
       </c>
       <c r="H139" s="22" t="n">
-        <v>0.1527196783988226</v>
+        <v>0.2275791642990199</v>
       </c>
       <c r="I139" s="5" t="n">
         <v>5</v>
@@ -7712,19 +7712,19 @@
         </is>
       </c>
       <c r="D140" s="22" t="n">
-        <v>1554.6</v>
+        <v>47</v>
       </c>
       <c r="E140" s="22" t="n">
-        <v>13.93915348936226</v>
+        <v>18.09696107085386</v>
       </c>
       <c r="F140" s="22" t="n">
-        <v>1537</v>
+        <v>21</v>
       </c>
       <c r="G140" s="22" t="n">
-        <v>1573</v>
+        <v>68</v>
       </c>
       <c r="H140" s="22" t="n">
-        <v>12.21820674239882</v>
+        <v>15.86268577511387</v>
       </c>
       <c r="I140" s="5" t="n">
         <v>5</v>
@@ -7747,19 +7747,19 @@
         </is>
       </c>
       <c r="D141" s="22" t="n">
-        <v>124.26226</v>
+        <v>406.45908</v>
       </c>
       <c r="E141" s="22" t="n">
-        <v>1.779476095090911</v>
+        <v>1.31155783593406</v>
       </c>
       <c r="F141" s="22" t="n">
-        <v>122.8826</v>
+        <v>405.5334</v>
       </c>
       <c r="G141" s="22" t="n">
-        <v>127.3484</v>
+        <v>408.7379</v>
       </c>
       <c r="H141" s="22" t="n">
-        <v>1.559779569079989</v>
+        <v>1.149631131207861</v>
       </c>
       <c r="I141" s="5" t="n">
         <v>5</v>
@@ -7782,19 +7782,19 @@
         </is>
       </c>
       <c r="D142" s="25" t="n">
-        <v>388358.1053</v>
+        <v>128190.88714</v>
       </c>
       <c r="E142" s="25" t="n">
-        <v>8358.420824673773</v>
+        <v>3094.411974536899</v>
       </c>
       <c r="F142" s="25" t="n">
-        <v>375159.0032</v>
+        <v>123292.9924</v>
       </c>
       <c r="G142" s="25" t="n">
-        <v>394727.9485</v>
+        <v>131729.2231</v>
       </c>
       <c r="H142" s="25" t="n">
-        <v>7326.478882219999</v>
+        <v>2712.371685977911</v>
       </c>
       <c r="I142" s="23" t="n">
         <v>5</v>
@@ -7817,19 +7817,19 @@
         </is>
       </c>
       <c r="D143" s="25" t="n">
-        <v>84.27312000000001</v>
+        <v>99.76740000000001</v>
       </c>
       <c r="E143" s="25" t="n">
-        <v>0.7434331657923281</v>
+        <v>0.1980282555596548</v>
       </c>
       <c r="F143" s="25" t="n">
-        <v>83.53489999999999</v>
+        <v>99.5539</v>
       </c>
       <c r="G143" s="25" t="n">
-        <v>85.3229</v>
+        <v>99.9567</v>
       </c>
       <c r="H143" s="25" t="n">
-        <v>0.6516479014122906</v>
+        <v>0.1735794192316588</v>
       </c>
       <c r="I143" s="23" t="n">
         <v>5</v>
@@ -7852,19 +7852,19 @@
         </is>
       </c>
       <c r="D144" s="25" t="n">
-        <v>951.8</v>
+        <v>16.6</v>
       </c>
       <c r="E144" s="25" t="n">
-        <v>52.45664876829247</v>
+        <v>14.36314728741581</v>
       </c>
       <c r="F144" s="25" t="n">
-        <v>871</v>
+        <v>3</v>
       </c>
       <c r="G144" s="25" t="n">
-        <v>996</v>
+        <v>32</v>
       </c>
       <c r="H144" s="25" t="n">
-        <v>45.98027994695116</v>
+        <v>12.58985369255735</v>
       </c>
       <c r="I144" s="23" t="n">
         <v>5</v>
@@ -7887,19 +7887,19 @@
         </is>
       </c>
       <c r="D145" s="25" t="n">
-        <v>119.17886</v>
+        <v>406.1277</v>
       </c>
       <c r="E145" s="25" t="n">
-        <v>1.641379172525348</v>
+        <v>1.898500013168292</v>
       </c>
       <c r="F145" s="25" t="n">
-        <v>116.6828</v>
+        <v>404.6365</v>
       </c>
       <c r="G145" s="25" t="n">
-        <v>121.2944</v>
+        <v>409.0521</v>
       </c>
       <c r="H145" s="25" t="n">
-        <v>1.438732279394661</v>
+        <v>1.66410863321359</v>
       </c>
       <c r="I145" s="23" t="n">
         <v>5</v>
@@ -7922,19 +7922,19 @@
         </is>
       </c>
       <c r="D146" s="22" t="n">
-        <v>676888.7525199999</v>
+        <v>742692.97098</v>
       </c>
       <c r="E146" s="22" t="n">
-        <v>58769.91022575272</v>
+        <v>58649.85711908941</v>
       </c>
       <c r="F146" s="22" t="n">
-        <v>605454.5876</v>
+        <v>678299.7057</v>
       </c>
       <c r="G146" s="22" t="n">
-        <v>731779.3631</v>
+        <v>835505.7077</v>
       </c>
       <c r="H146" s="22" t="n">
-        <v>51514.09760416649</v>
+        <v>51408.86641646208</v>
       </c>
       <c r="I146" s="5" t="n">
         <v>5</v>
@@ -7957,19 +7957,19 @@
         </is>
       </c>
       <c r="D147" s="22" t="n">
-        <v>87.71088</v>
+        <v>87.47286000000001</v>
       </c>
       <c r="E147" s="22" t="n">
-        <v>0.8332398256204497</v>
+        <v>1.416817579295231</v>
       </c>
       <c r="F147" s="22" t="n">
-        <v>86.8806</v>
+        <v>85.253</v>
       </c>
       <c r="G147" s="22" t="n">
-        <v>88.8329</v>
+        <v>89.0971</v>
       </c>
       <c r="H147" s="22" t="n">
-        <v>0.7303669095257793</v>
+        <v>1.241895364256167</v>
       </c>
       <c r="I147" s="5" t="n">
         <v>5</v>
@@ -7992,19 +7992,19 @@
         </is>
       </c>
       <c r="D148" s="22" t="n">
-        <v>729.6</v>
+        <v>814.6</v>
       </c>
       <c r="E148" s="22" t="n">
-        <v>44.43309577330844</v>
+        <v>91.26499876732591</v>
       </c>
       <c r="F148" s="22" t="n">
-        <v>662</v>
+        <v>720</v>
       </c>
       <c r="G148" s="22" t="n">
-        <v>771</v>
+        <v>963</v>
       </c>
       <c r="H148" s="22" t="n">
-        <v>38.94732565915149</v>
+        <v>79.99729855438868</v>
       </c>
       <c r="I148" s="5" t="n">
         <v>5</v>
@@ -8027,19 +8027,19 @@
         </is>
       </c>
       <c r="D149" s="22" t="n">
-        <v>99.37642000000001</v>
+        <v>98.85538</v>
       </c>
       <c r="E149" s="22" t="n">
-        <v>2.069926365115439</v>
+        <v>3.030629770691236</v>
       </c>
       <c r="F149" s="22" t="n">
-        <v>96.1895</v>
+        <v>93.8997</v>
       </c>
       <c r="G149" s="22" t="n">
-        <v>101.3015</v>
+        <v>101.4147</v>
       </c>
       <c r="H149" s="22" t="n">
-        <v>1.814370455840331</v>
+        <v>2.656464119304879</v>
       </c>
       <c r="I149" s="5" t="n">
         <v>5</v>
@@ -8549,25 +8549,25 @@
         </is>
       </c>
       <c r="C2" s="7" t="n">
-        <v>11.76711598</v>
+        <v>55.2697481</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>6.13973112</v>
+        <v>54.47583742</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>0.3678087</v>
+        <v>0.3991506399999999</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>5.259576139999999</v>
-      </c>
-      <c r="G2" s="10" t="n">
-        <v>52.17702562323176</v>
-      </c>
-      <c r="H2" s="10" t="n">
-        <v>3.125733617524862</v>
-      </c>
-      <c r="I2" s="10" t="n">
-        <v>44.69724058927819</v>
+        <v>0.3947599999999999</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>98.56357101797609</v>
+      </c>
+      <c r="H2" s="9" t="n">
+        <v>0.7221864649678038</v>
+      </c>
+      <c r="I2" s="9" t="n">
+        <v>0.7142424446837671</v>
       </c>
     </row>
     <row r="3">
@@ -8582,25 +8582,25 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>264.2273326599999</v>
+        <v>65.73206165999999</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>23.90818116</v>
+        <v>49.17661678</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>89.21336669999999</v>
+        <v>0.06035514000000001</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>151.10578484</v>
-      </c>
-      <c r="G3" s="10" t="n">
-        <v>9.048337626283482</v>
-      </c>
-      <c r="H3" s="10" t="n">
-        <v>33.76386757640898</v>
-      </c>
-      <c r="I3" s="10" t="n">
-        <v>57.18779481244606</v>
+        <v>16.49508974</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>74.81374467511263</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>0.09181994064355962</v>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>25.09443538424382</v>
       </c>
     </row>
     <row r="4">
@@ -8615,25 +8615,25 @@
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>262.18504354</v>
+        <v>65.7692102</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>23.93227908</v>
+        <v>49.17661678</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>86.06631780000001</v>
+        <v>0.06035514000000001</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>152.1864466</v>
-      </c>
-      <c r="G4" s="10" t="n">
-        <v>9.128010796065411</v>
-      </c>
-      <c r="H4" s="10" t="n">
-        <v>32.82655510701143</v>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>58.04543407403856</v>
+        <v>16.53223828</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>74.7714874946149</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>0.0917680778231392</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>25.13674442756194</v>
       </c>
     </row>
     <row r="5">
@@ -8648,25 +8648,25 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>294.1235757600001</v>
+        <v>83.12825875999999</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>23.59982202</v>
+        <v>49.8675074</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>122.03531422</v>
+        <v>2.4181795</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>148.48843954</v>
+        <v>30.84257186</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>8.02377774682607</v>
+        <v>59.98863460375458</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>41.49117047304593</v>
+        <v>2.908974079418093</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>50.48505178692785</v>
+        <v>37.10239131682734</v>
       </c>
     </row>
     <row r="6">
@@ -8681,25 +8681,25 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>71.59054244000001</v>
+        <v>73.94904883999999</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>6.06378982</v>
+        <v>73.90693710000001</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>5.02370976</v>
+        <v>0.02501176</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>60.50304286000001</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>8.470099000970777</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>7.017281317864532</v>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>84.51261968116469</v>
+        <v>0.0171</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>99.94305303359467</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>0.03382296377349862</v>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>0.02312402967751276</v>
       </c>
     </row>
     <row r="7">
@@ -8714,25 +8714,25 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>105.43504684</v>
+        <v>71.54982554</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>7.67508842</v>
+        <v>69.27616822000002</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>60.65160162000001</v>
+        <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>37.10835682</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>7.279447062462176</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>57.52508623820326</v>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>35.19546671830359</v>
+        <v>2.27365732</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>96.82227412458344</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>3.177725875416579</v>
       </c>
     </row>
     <row r="8">
@@ -8747,25 +8747,25 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>109.94782728</v>
+        <v>71.54982554</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>7.71519106</v>
+        <v>69.27616822000002</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>61.05557438</v>
+        <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>41.17706186</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>7.01713826536291</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>55.53140602270572</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>37.45145573012182</v>
+        <v>2.27365732</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>96.82227412458344</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>3.177725875416579</v>
       </c>
     </row>
     <row r="9">
@@ -8780,25 +8780,25 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>116.94121104</v>
+        <v>74.44927092</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>10.69314606</v>
+        <v>71.93342259999999</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>4.33062404</v>
+        <v>0</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>101.91744094</v>
+        <v>2.51584832</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>9.144035678185672</v>
+        <v>96.62072134634677</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>3.703248838870585</v>
+        <v>0</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>87.15271548294375</v>
+        <v>3.3792786536532</v>
       </c>
     </row>
     <row r="10">
@@ -8813,25 +8813,25 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>174.95273972</v>
+        <v>87.47367942</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>7.8576666</v>
+        <v>86.04352257999999</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>41.9216724</v>
+        <v>0.6861968200000002</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>125.17340074</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>4.491308117023867</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>23.96171244136719</v>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>71.54697945304059</v>
+        <v>0.74396</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>98.36504323416739</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>0.784460908183894</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>0.8504958347846755</v>
       </c>
     </row>
     <row r="11">
@@ -8846,25 +8846,25 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>364.80710478</v>
+        <v>102.41096022</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>29.80146216</v>
+        <v>87.35791193999999</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>77.06578978</v>
+        <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>257.93985284</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>8.169101360559308</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>21.1250791912277</v>
-      </c>
-      <c r="I11" s="10" t="n">
-        <v>70.70581944821299</v>
+        <v>15.05304832</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>85.3013307875808</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>14.69866925147751</v>
       </c>
     </row>
     <row r="12">
@@ -8879,25 +8879,25 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>367.80324106</v>
+        <v>101.42445222</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>29.81291558</v>
+        <v>87.28998496</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>79.00705425999999</v>
+        <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>258.98327118</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <v>8.10566962218166</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>21.48079338080425</v>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>70.41353698613869</v>
+        <v>14.13446724</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>86.06404377778556</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>13.93595620249533</v>
       </c>
     </row>
     <row r="13">
@@ -8912,25 +8912,25 @@
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>417.67333198</v>
+        <v>90.36350659999999</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>31.28593048</v>
+        <v>85.85423072</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>108.81087922</v>
+        <v>0</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>277.57652228</v>
+        <v>4.509275879999999</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>7.49052622816199</v>
+        <v>95.00984850005811</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>26.05167026206268</v>
+        <v>0</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>66.45780350977533</v>
+        <v>4.990151499941902</v>
       </c>
     </row>
     <row r="14">
@@ -8945,25 +8945,25 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>170.82634104</v>
+        <v>213.48660962</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>12.60385112</v>
+        <v>13.74088662</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>27.38079952</v>
+        <v>17.30659306</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>130.8416904</v>
-      </c>
-      <c r="G14" s="10" t="n">
-        <v>7.378166062251916</v>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>16.02844113694891</v>
-      </c>
-      <c r="I14" s="10" t="n">
-        <v>76.59339280079915</v>
+        <v>182.43912996</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>6.436416150154982</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>8.106641016410929</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>85.45694284280235</v>
       </c>
     </row>
     <row r="15">
@@ -8978,25 +8978,25 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>209.89549308</v>
+        <v>207.66048284</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>14.84267522</v>
+        <v>14.83764562</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>127.99090924</v>
+        <v>127.50501856</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>67.06190866</v>
-      </c>
-      <c r="G15" s="10" t="n">
-        <v>7.071459707018499</v>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>60.97839804078941</v>
-      </c>
-      <c r="I15" s="10" t="n">
-        <v>31.95014227124919</v>
+        <v>65.31781866</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>7.145146451109928</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>61.40071371125585</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>31.45413983763422</v>
       </c>
     </row>
     <row r="16">
@@ -9022,13 +9022,13 @@
       <c r="F16" s="7" t="n">
         <v>96.23181428000001</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="G16" s="9" t="n">
         <v>6.383056097551044</v>
       </c>
-      <c r="H16" s="10" t="n">
+      <c r="H16" s="9" t="n">
         <v>55.2423951295556</v>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="I16" s="9" t="n">
         <v>38.37454878086881</v>
       </c>
     </row>
@@ -9088,13 +9088,13 @@
       <c r="F18" s="7" t="n">
         <v>261.63472036</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="G18" s="9" t="n">
         <v>4.226513358542875</v>
       </c>
-      <c r="H18" s="10" t="n">
+      <c r="H18" s="9" t="n">
         <v>25.84667245403036</v>
       </c>
-      <c r="I18" s="10" t="n">
+      <c r="I18" s="9" t="n">
         <v>69.92681419811751</v>
       </c>
     </row>
@@ -9121,13 +9121,13 @@
       <c r="F19" s="7" t="n">
         <v>174.54830578</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="G19" s="9" t="n">
         <v>5.240788047872426</v>
       </c>
-      <c r="H19" s="10" t="n">
+      <c r="H19" s="9" t="n">
         <v>47.31136324617644</v>
       </c>
-      <c r="I19" s="10" t="n">
+      <c r="I19" s="9" t="n">
         <v>47.44784870051448</v>
       </c>
     </row>
@@ -9154,13 +9154,13 @@
       <c r="F20" s="7" t="n">
         <v>169.0111578</v>
       </c>
-      <c r="G20" s="10" t="n">
+      <c r="G20" s="9" t="n">
         <v>5.33113415145637</v>
       </c>
-      <c r="H20" s="10" t="n">
+      <c r="H20" s="9" t="n">
         <v>47.90749310488459</v>
       </c>
-      <c r="I20" s="10" t="n">
+      <c r="I20" s="9" t="n">
         <v>46.76137274365906</v>
       </c>
     </row>
@@ -9220,13 +9220,13 @@
       <c r="F22" s="7" t="n">
         <v>542.29926098</v>
       </c>
-      <c r="G22" s="10" t="n">
+      <c r="G22" s="9" t="n">
         <v>3.282210218370778</v>
       </c>
-      <c r="H22" s="10" t="n">
+      <c r="H22" s="9" t="n">
         <v>35.45985968916357</v>
       </c>
-      <c r="I22" s="10" t="n">
+      <c r="I22" s="9" t="n">
         <v>61.25793009020647</v>
       </c>
     </row>
@@ -9253,13 +9253,13 @@
       <c r="F23" s="7" t="n">
         <v>323.0544920200001</v>
       </c>
-      <c r="G23" s="10" t="n">
+      <c r="G23" s="9" t="n">
         <v>4.422243605274225</v>
       </c>
-      <c r="H23" s="10" t="n">
+      <c r="H23" s="9" t="n">
         <v>42.77019589924552</v>
       </c>
-      <c r="I23" s="10" t="n">
+      <c r="I23" s="9" t="n">
         <v>52.80756049874954</v>
       </c>
     </row>
@@ -9286,13 +9286,13 @@
       <c r="F24" s="7" t="n">
         <v>319.7046719</v>
       </c>
-      <c r="G24" s="10" t="n">
+      <c r="G24" s="9" t="n">
         <v>4.47636085179698</v>
       </c>
-      <c r="H24" s="10" t="n">
+      <c r="H24" s="9" t="n">
         <v>42.26945934585512</v>
       </c>
-      <c r="I24" s="10" t="n">
+      <c r="I24" s="9" t="n">
         <v>53.2541798023479</v>
       </c>
     </row>
@@ -9352,13 +9352,13 @@
       <c r="F26" s="7" t="n">
         <v>901.5594978199999</v>
       </c>
-      <c r="G26" s="10" t="n">
+      <c r="G26" s="9" t="n">
         <v>3.216858588527266</v>
       </c>
-      <c r="H26" s="10" t="n">
+      <c r="H26" s="9" t="n">
         <v>40.31544811126466</v>
       </c>
-      <c r="I26" s="10" t="n">
+      <c r="I26" s="9" t="n">
         <v>56.46769329770274</v>
       </c>
     </row>
@@ -9385,13 +9385,13 @@
       <c r="F27" s="7" t="n">
         <v>472.37459332</v>
       </c>
-      <c r="G27" s="10" t="n">
+      <c r="G27" s="9" t="n">
         <v>4.147606928490591</v>
       </c>
-      <c r="H27" s="10" t="n">
+      <c r="H27" s="9" t="n">
         <v>40.05332434552531</v>
       </c>
-      <c r="I27" s="10" t="n">
+      <c r="I27" s="9" t="n">
         <v>55.7990687283466</v>
       </c>
     </row>
@@ -9418,13 +9418,13 @@
       <c r="F28" s="7" t="n">
         <v>476.70506316</v>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="G28" s="9" t="n">
         <v>4.110577472285466</v>
       </c>
-      <c r="H28" s="10" t="n">
+      <c r="H28" s="9" t="n">
         <v>40.19053182417202</v>
       </c>
-      <c r="I28" s="10" t="n">
+      <c r="I28" s="9" t="n">
         <v>55.69889070120568</v>
       </c>
     </row>
@@ -9473,25 +9473,25 @@
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>56.282888</v>
+        <v>88.71947573999999</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>24.09047462</v>
+        <v>25.37531756</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>1.70919442</v>
+        <v>1.88402608</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>30.48321898</v>
-      </c>
-      <c r="G30" s="10" t="n">
-        <v>42.80248486893565</v>
-      </c>
-      <c r="H30" s="10" t="n">
-        <v>3.036792319541243</v>
-      </c>
-      <c r="I30" s="10" t="n">
-        <v>54.1607228470579</v>
+        <v>61.46013212000001</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>28.60174426003659</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>2.123576660350541</v>
+      </c>
+      <c r="I30" s="9" t="n">
+        <v>69.27467910215586</v>
       </c>
     </row>
     <row r="31">
@@ -9517,13 +9517,13 @@
       <c r="F31" s="7" t="n">
         <v>4.87681812</v>
       </c>
-      <c r="G31" s="10" t="n">
+      <c r="G31" s="9" t="n">
         <v>16.94730740871955</v>
       </c>
-      <c r="H31" s="10" t="n">
+      <c r="H31" s="9" t="n">
         <v>80.07147484977646</v>
       </c>
-      <c r="I31" s="10" t="n">
+      <c r="I31" s="9" t="n">
         <v>2.981217717051821</v>
       </c>
     </row>
@@ -9550,13 +9550,13 @@
       <c r="F32" s="7" t="n">
         <v>4.87681812</v>
       </c>
-      <c r="G32" s="10" t="n">
+      <c r="G32" s="9" t="n">
         <v>16.94730740871955</v>
       </c>
-      <c r="H32" s="10" t="n">
+      <c r="H32" s="9" t="n">
         <v>80.07147484977646</v>
       </c>
-      <c r="I32" s="10" t="n">
+      <c r="I32" s="9" t="n">
         <v>2.981217717051821</v>
       </c>
     </row>
@@ -9605,25 +9605,25 @@
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>332.46828218</v>
+        <v>142.65096726</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>24.84263468</v>
+        <v>96.32759774</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>44.84028470000001</v>
+        <v>4.853140420000001</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>262.78536276</v>
-      </c>
-      <c r="G34" s="10" t="n">
-        <v>7.472181862614513</v>
-      </c>
-      <c r="H34" s="10" t="n">
-        <v>13.48708646911565</v>
-      </c>
-      <c r="I34" s="10" t="n">
-        <v>79.04073165623862</v>
+        <v>41.47022912</v>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>67.52677503015481</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>3.402108315995165</v>
+      </c>
+      <c r="I34" s="9" t="n">
+        <v>29.07111666787025</v>
       </c>
     </row>
     <row r="35">
@@ -9638,25 +9638,25 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>431.01602148</v>
+        <v>116.82890448</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>30.5027677</v>
+        <v>105.5904818</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>279.03972294</v>
+        <v>1.49272928</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>121.47353088</v>
-      </c>
-      <c r="G35" s="10" t="n">
-        <v>7.076945213141084</v>
-      </c>
-      <c r="H35" s="10" t="n">
-        <v>64.73998854656219</v>
-      </c>
-      <c r="I35" s="10" t="n">
-        <v>28.18306624957713</v>
+        <v>9.7456934</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>90.38044332434538</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>1.277705450242873</v>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>8.341851225411748</v>
       </c>
     </row>
     <row r="36">
@@ -9671,25 +9671,25 @@
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>411.42811356</v>
+        <v>116.82890448</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>30.54658728</v>
+        <v>105.5904818</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>267.95136508</v>
+        <v>1.49272928</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>112.93016116</v>
-      </c>
-      <c r="G36" s="10" t="n">
-        <v>7.424526004236045</v>
-      </c>
-      <c r="H36" s="10" t="n">
-        <v>65.12714037975525</v>
-      </c>
-      <c r="I36" s="10" t="n">
-        <v>27.44833360628649</v>
+        <v>9.7456934</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>90.38044332434538</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>1.277705450242873</v>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>8.341851225411748</v>
       </c>
     </row>
     <row r="37">
@@ -9704,25 +9704,25 @@
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>388.3581053</v>
+        <v>128.19088714</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>35.31548046</v>
+        <v>113.51797724</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>206.8393081</v>
+        <v>1.50974826</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>146.20331672</v>
+        <v>13.1631617</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>9.093535059019663</v>
+        <v>88.55385883711421</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>53.25994366468036</v>
+        <v>1.177734465907215</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>37.6465212711501</v>
+        <v>10.26840674378377</v>
       </c>
     </row>
     <row r="38">
@@ -9737,25 +9737,25 @@
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>676.8887525199999</v>
+        <v>742.6929709799999</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>30.26819418</v>
+        <v>34.48558516</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>154.42127682</v>
+        <v>165.0826961</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>492.19928152</v>
-      </c>
-      <c r="G38" s="10" t="n">
-        <v>4.471664519068172</v>
-      </c>
-      <c r="H38" s="10" t="n">
-        <v>22.81339086298931</v>
-      </c>
-      <c r="I38" s="10" t="n">
-        <v>72.71494461794254</v>
+        <v>543.1246897</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>4.643316485747199</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>22.22758293809752</v>
+      </c>
+      <c r="I38" s="9" t="n">
+        <v>73.12910057346238</v>
       </c>
     </row>
     <row r="39">
@@ -9781,13 +9781,13 @@
       <c r="F39" s="7" t="n">
         <v>334.5561998</v>
       </c>
-      <c r="G39" s="10" t="n">
+      <c r="G39" s="9" t="n">
         <v>5.367989221744614</v>
       </c>
-      <c r="H39" s="10" t="n">
+      <c r="H39" s="9" t="n">
         <v>47.82656072450715</v>
       </c>
-      <c r="I39" s="10" t="n">
+      <c r="I39" s="9" t="n">
         <v>46.80545005934438</v>
       </c>
     </row>
@@ -9814,13 +9814,13 @@
       <c r="F40" s="7" t="n">
         <v>345.3648986600001</v>
       </c>
-      <c r="G40" s="10" t="n">
+      <c r="G40" s="9" t="n">
         <v>5.281664323816845</v>
       </c>
-      <c r="H40" s="10" t="n">
+      <c r="H40" s="9" t="n">
         <v>46.94046926002591</v>
       </c>
-      <c r="I40" s="10" t="n">
+      <c r="I40" s="9" t="n">
         <v>47.77786641615725</v>
       </c>
     </row>
@@ -9950,25 +9950,25 @@
         <v>1</v>
       </c>
       <c r="D2" s="22" t="n">
-        <v>14407.979</v>
+        <v>54955.6124</v>
       </c>
       <c r="E2" s="22" t="n">
-        <v>95.1096</v>
+        <v>97.15649999999999</v>
       </c>
       <c r="F2" s="15" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G2" s="22" t="n">
-        <v>309.4148</v>
+        <v>1233.9499</v>
       </c>
       <c r="H2" s="22" t="n">
-        <v>6171.8224</v>
+        <v>54042.1143</v>
       </c>
       <c r="I2" s="22" t="n">
-        <v>404.1334</v>
+        <v>467.398</v>
       </c>
       <c r="J2" s="22" t="n">
-        <v>7832.0232</v>
+        <v>446.1</v>
       </c>
     </row>
     <row r="3">
@@ -9986,25 +9986,25 @@
         <v>2</v>
       </c>
       <c r="D3" s="22" t="n">
-        <v>15573.6263</v>
+        <v>55049.6025</v>
       </c>
       <c r="E3" s="22" t="n">
-        <v>95.5633</v>
+        <v>98.35890000000001</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G3" s="22" t="n">
-        <v>305.328</v>
+        <v>1240.8372</v>
       </c>
       <c r="H3" s="22" t="n">
-        <v>6051.4992</v>
+        <v>54420.294</v>
       </c>
       <c r="I3" s="22" t="n">
-        <v>403.9497</v>
+        <v>256.6085</v>
       </c>
       <c r="J3" s="22" t="n">
-        <v>9118.1774</v>
+        <v>372.7</v>
       </c>
     </row>
     <row r="4">
@@ -10022,25 +10022,25 @@
         <v>3</v>
       </c>
       <c r="D4" s="22" t="n">
-        <v>14825.8421</v>
+        <v>55856.4083</v>
       </c>
       <c r="E4" s="22" t="n">
-        <v>94.6785</v>
+        <v>98.09</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G4" s="22" t="n">
-        <v>306.0823</v>
+        <v>1252.626</v>
       </c>
       <c r="H4" s="22" t="n">
-        <v>6114.6633</v>
+        <v>55154.7119</v>
       </c>
       <c r="I4" s="22" t="n">
-        <v>422.2986</v>
+        <v>353.7964</v>
       </c>
       <c r="J4" s="22" t="n">
-        <v>8288.8801</v>
+        <v>347.9</v>
       </c>
     </row>
     <row r="5">
@@ -10058,25 +10058,25 @@
         <v>4</v>
       </c>
       <c r="D5" s="22" t="n">
-        <v>7091.4904</v>
+        <v>55514.7142</v>
       </c>
       <c r="E5" s="22" t="n">
-        <v>96.1442</v>
+        <v>97.3404</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G5" s="22" t="n">
-        <v>314.8135</v>
+        <v>1243.9871</v>
       </c>
       <c r="H5" s="22" t="n">
-        <v>6287.4096</v>
+        <v>54524.425</v>
       </c>
       <c r="I5" s="22" t="n">
-        <v>295.7808</v>
+        <v>575.6892</v>
       </c>
       <c r="J5" s="22" t="n">
-        <v>508.3</v>
+        <v>414.6</v>
       </c>
     </row>
     <row r="6">
@@ -10094,25 +10094,25 @@
         <v>5</v>
       </c>
       <c r="D6" s="22" t="n">
-        <v>6936.6421</v>
+        <v>54972.4031</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>96.13120000000001</v>
+        <v>97.76430000000001</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G6" s="22" t="n">
-        <v>306.444</v>
+        <v>1238.3303</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>6073.2611</v>
+        <v>54237.6419</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>312.881</v>
+        <v>342.2611</v>
       </c>
       <c r="J6" s="22" t="n">
-        <v>550.5</v>
+        <v>392.5</v>
       </c>
     </row>
     <row r="7">
@@ -10130,25 +10130,25 @@
         <v>1</v>
       </c>
       <c r="D7" s="22" t="n">
-        <v>265843.8376</v>
+        <v>66213.7064</v>
       </c>
       <c r="E7" s="22" t="n">
-        <v>76.92310000000001</v>
+        <v>100</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="G7" s="22" t="n">
-        <v>534.5667999999999</v>
+        <v>1364.1642</v>
       </c>
       <c r="H7" s="22" t="n">
-        <v>24091.6863</v>
+        <v>49209.6139</v>
       </c>
       <c r="I7" s="22" t="n">
-        <v>84441.7819</v>
+        <v>131.4435</v>
       </c>
       <c r="J7" s="22" t="n">
-        <v>157310.3695</v>
+        <v>16872.649</v>
       </c>
     </row>
     <row r="8">
@@ -10166,25 +10166,25 @@
         <v>2</v>
       </c>
       <c r="D8" s="22" t="n">
-        <v>280502.0414</v>
+        <v>67224.15760000001</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>74.02500000000001</v>
+        <v>100</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="G8" s="22" t="n">
-        <v>527.4502</v>
+        <v>1359.8656</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>23657.4064</v>
+        <v>48930.0813</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>103272.8299</v>
+        <v>66.6908</v>
       </c>
       <c r="J8" s="22" t="n">
-        <v>153571.8051</v>
+        <v>18227.3855</v>
       </c>
     </row>
     <row r="9">
@@ -10202,25 +10202,25 @@
         <v>3</v>
       </c>
       <c r="D9" s="22" t="n">
-        <v>269912.7554</v>
+        <v>64817.0903</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>75.946</v>
+        <v>100</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>525.9979</v>
+        <v>1360.4446</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>23559.4896</v>
+        <v>49081.714</v>
       </c>
       <c r="I9" s="22" t="n">
-        <v>94858.87480000001</v>
+        <v>60.9741</v>
       </c>
       <c r="J9" s="22" t="n">
-        <v>151494.3911</v>
+        <v>15674.4022</v>
       </c>
     </row>
     <row r="10">
@@ -10238,25 +10238,25 @@
         <v>4</v>
       </c>
       <c r="D10" s="22" t="n">
-        <v>252901.0818</v>
+        <v>65748.22809999999</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>79.5521</v>
+        <v>100</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>538.4769</v>
+        <v>1369.4755</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>24207.4457</v>
+        <v>49379.5251</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>80498.0341</v>
+        <v>40.0464</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>148195.602</v>
+        <v>16328.6566</v>
       </c>
     </row>
     <row r="11">
@@ -10274,25 +10274,25 @@
         <v>5</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>251976.9471</v>
+        <v>64657.1259</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>76.8211</v>
+        <v>100</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="G11" s="22" t="n">
-        <v>534.7545</v>
+        <v>1369.9126</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>24024.8778</v>
+        <v>49282.1496</v>
       </c>
       <c r="I11" s="22" t="n">
-        <v>82995.3128</v>
+        <v>2.6209</v>
       </c>
       <c r="J11" s="22" t="n">
-        <v>144956.7565</v>
+        <v>15372.3554</v>
       </c>
     </row>
     <row r="12">
@@ -10310,25 +10310,25 @@
         <v>1</v>
       </c>
       <c r="D12" s="22" t="n">
-        <v>264644.9271</v>
+        <v>66247.0528</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>77.6841</v>
+        <v>100</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>535.7977</v>
+        <v>1364.1642</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>24150.0521</v>
+        <v>49209.6139</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>81367.8466</v>
+        <v>131.4435</v>
       </c>
       <c r="J12" s="22" t="n">
-        <v>159127.0284</v>
+        <v>16905.9955</v>
       </c>
     </row>
     <row r="13">
@@ -10346,25 +10346,25 @@
         <v>2</v>
       </c>
       <c r="D13" s="22" t="n">
-        <v>280428.6799</v>
+        <v>67275.3553</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>74.4224</v>
+        <v>100</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>527.5962</v>
+        <v>1359.8656</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>23661.9511</v>
+        <v>48930.0813</v>
       </c>
       <c r="I13" s="22" t="n">
-        <v>102457.0139</v>
+        <v>66.6908</v>
       </c>
       <c r="J13" s="22" t="n">
-        <v>154309.7148</v>
+        <v>18278.5832</v>
       </c>
     </row>
     <row r="14">
@@ -10382,25 +10382,25 @@
         <v>3</v>
       </c>
       <c r="D14" s="22" t="n">
-        <v>262293.5259</v>
+        <v>64852.6497</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>77.96120000000001</v>
+        <v>100</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>527.7826</v>
+        <v>1360.4446</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>23697.2914</v>
+        <v>49081.714</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>90569.0624</v>
+        <v>60.9741</v>
       </c>
       <c r="J14" s="22" t="n">
-        <v>148027.1721</v>
+        <v>15709.9616</v>
       </c>
     </row>
     <row r="15">
@@ -10418,25 +10418,25 @@
         <v>4</v>
       </c>
       <c r="D15" s="22" t="n">
-        <v>254568.2506</v>
+        <v>65784.6678</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>80.1319</v>
+        <v>100</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>538.6328</v>
+        <v>1369.4755</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>24231.8595</v>
+        <v>49379.5251</v>
       </c>
       <c r="I15" s="22" t="n">
-        <v>79867.99310000001</v>
+        <v>40.0464</v>
       </c>
       <c r="J15" s="22" t="n">
-        <v>150468.3979</v>
+        <v>16365.0963</v>
       </c>
     </row>
     <row r="16">
@@ -10454,25 +10454,25 @@
         <v>5</v>
       </c>
       <c r="D16" s="22" t="n">
-        <v>248989.8342</v>
+        <v>64686.3254</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>79.04170000000001</v>
+        <v>100</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>532.1756</v>
+        <v>1369.9126</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>23920.2413</v>
+        <v>49282.1496</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>76069.673</v>
+        <v>2.6209</v>
       </c>
       <c r="J16" s="22" t="n">
-        <v>148999.9198</v>
+        <v>15401.5548</v>
       </c>
     </row>
     <row r="17">
@@ -10490,25 +10490,25 @@
         <v>1</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>315991.7867</v>
+        <v>82449.06080000001</v>
       </c>
       <c r="E17" s="25" t="n">
-        <v>57.4001</v>
+        <v>98.47239999999999</v>
       </c>
       <c r="F17" s="26" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="G17" s="25" t="n">
-        <v>528.1279</v>
+        <v>1364.8188</v>
       </c>
       <c r="H17" s="25" t="n">
-        <v>23756.4581</v>
+        <v>49845.6244</v>
       </c>
       <c r="I17" s="25" t="n">
-        <v>136489.4836</v>
+        <v>2471.6939</v>
       </c>
       <c r="J17" s="25" t="n">
-        <v>155745.845</v>
+        <v>30131.7425</v>
       </c>
     </row>
     <row r="18">
@@ -10526,25 +10526,25 @@
         <v>2</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>292531.0726</v>
+        <v>86003.7251</v>
       </c>
       <c r="E18" s="25" t="n">
-        <v>58.684</v>
+        <v>98.92749999999999</v>
       </c>
       <c r="F18" s="26" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="G18" s="25" t="n">
-        <v>516.0865</v>
+        <v>1359.3172</v>
       </c>
       <c r="H18" s="25" t="n">
-        <v>23145.0536</v>
+        <v>49636.9232</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>122192.8883</v>
+        <v>2266.2421</v>
       </c>
       <c r="J18" s="25" t="n">
-        <v>147193.1308</v>
+        <v>34100.5598</v>
       </c>
     </row>
     <row r="19">
@@ -10562,25 +10562,25 @@
         <v>3</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>288761.3118</v>
+        <v>85856.08040000001</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>63.6452</v>
+        <v>98.1159</v>
       </c>
       <c r="F19" s="26" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G19" s="25" t="n">
-        <v>525.9348</v>
+        <v>1357.3215</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>23811.4918</v>
+        <v>49866.4995</v>
       </c>
       <c r="I19" s="25" t="n">
-        <v>114392.0068</v>
+        <v>3157.2145</v>
       </c>
       <c r="J19" s="25" t="n">
-        <v>150557.8132</v>
+        <v>32832.3664</v>
       </c>
     </row>
     <row r="20">
@@ -10598,25 +10598,25 @@
         <v>4</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>281582.3653</v>
+        <v>79519.21000000001</v>
       </c>
       <c r="E20" s="25" t="n">
-        <v>61.0975</v>
+        <v>98.71599999999999</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="G20" s="25" t="n">
-        <v>530.8414</v>
+        <v>1367.7311</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>23871.7336</v>
+        <v>49917.5179</v>
       </c>
       <c r="I20" s="25" t="n">
-        <v>115028.2378</v>
+        <v>1897.1521</v>
       </c>
       <c r="J20" s="25" t="n">
-        <v>142682.3939</v>
+        <v>27704.54</v>
       </c>
     </row>
     <row r="21">
@@ -10634,25 +10634,25 @@
         <v>5</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>291751.3424</v>
+        <v>81813.2175</v>
       </c>
       <c r="E21" s="25" t="n">
-        <v>60.3914</v>
+        <v>98.6901</v>
       </c>
       <c r="F21" s="26" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="G21" s="25" t="n">
-        <v>520.4438</v>
+        <v>1366.5246</v>
       </c>
       <c r="H21" s="25" t="n">
-        <v>23414.373</v>
+        <v>50070.972</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>122073.9546</v>
+        <v>2298.5949</v>
       </c>
       <c r="J21" s="25" t="n">
-        <v>146263.0148</v>
+        <v>29443.6506</v>
       </c>
     </row>
     <row r="22">
@@ -10670,25 +10670,25 @@
         <v>1</v>
       </c>
       <c r="D22" s="22" t="n">
-        <v>73292.0043</v>
+        <v>73134.618</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>90.7366</v>
+        <v>99.80249999999999</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>109</v>
+        <v>4</v>
       </c>
       <c r="G22" s="22" t="n">
-        <v>124.4403</v>
+        <v>1079.0749</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>5825.5237</v>
+        <v>73031.54459999999</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>4184.1697</v>
+        <v>74.57340000000001</v>
       </c>
       <c r="J22" s="22" t="n">
-        <v>63282.3109</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="23">
@@ -10706,25 +10706,25 @@
         <v>2</v>
       </c>
       <c r="D23" s="22" t="n">
-        <v>85621.4614</v>
+        <v>74219.823</v>
       </c>
       <c r="E23" s="22" t="n">
-        <v>90.50749999999999</v>
+        <v>99.9534</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G23" s="22" t="n">
-        <v>128.9961</v>
+        <v>1090.9231</v>
       </c>
       <c r="H23" s="22" t="n">
-        <v>6253.6267</v>
+        <v>74192.1493</v>
       </c>
       <c r="I23" s="22" t="n">
-        <v>11289.2678</v>
+        <v>10.5737</v>
       </c>
       <c r="J23" s="22" t="n">
-        <v>68078.56690000001</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="24">
@@ -10742,25 +10742,25 @@
         <v>3</v>
       </c>
       <c r="D24" s="22" t="n">
-        <v>67036.624</v>
+        <v>74599.13959999999</v>
       </c>
       <c r="E24" s="22" t="n">
-        <v>92.4457</v>
+        <v>99.9004</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
       <c r="G24" s="22" t="n">
-        <v>126.8768</v>
+        <v>1092.7467</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>5979.4265</v>
+        <v>74564.3365</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>2732.3223</v>
+        <v>17.7032</v>
       </c>
       <c r="J24" s="22" t="n">
-        <v>58324.8752</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="25">
@@ -10778,25 +10778,25 @@
         <v>4</v>
       </c>
       <c r="D25" s="22" t="n">
-        <v>62526.9851</v>
+        <v>73191.50659999999</v>
       </c>
       <c r="E25" s="22" t="n">
-        <v>92.50660000000001</v>
+        <v>99.8035</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="G25" s="22" t="n">
-        <v>126.7651</v>
+        <v>1080.1222</v>
       </c>
       <c r="H25" s="22" t="n">
-        <v>6016.4087</v>
+        <v>73146.4981</v>
       </c>
       <c r="I25" s="22" t="n">
-        <v>2905.4131</v>
+        <v>22.2085</v>
       </c>
       <c r="J25" s="22" t="n">
-        <v>53605.1633</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="26">
@@ -10814,25 +10814,25 @@
         <v>5</v>
       </c>
       <c r="D26" s="22" t="n">
-        <v>69475.63740000001</v>
+        <v>74600.15700000001</v>
       </c>
       <c r="E26" s="22" t="n">
-        <v>92.1863</v>
+        <v>100</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="G26" s="22" t="n">
-        <v>131.0979</v>
+        <v>1091.3737</v>
       </c>
       <c r="H26" s="22" t="n">
-        <v>6243.9635</v>
+        <v>74600.15700000001</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>4007.3759</v>
+        <v>0</v>
       </c>
       <c r="J26" s="22" t="n">
-        <v>59224.298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -10850,25 +10850,25 @@
         <v>1</v>
       </c>
       <c r="D27" s="22" t="n">
-        <v>110531.9235</v>
+        <v>71222.51609999999</v>
       </c>
       <c r="E27" s="22" t="n">
-        <v>77.7456</v>
+        <v>100</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="G27" s="22" t="n">
-        <v>138.8735</v>
+        <v>1112.2753</v>
       </c>
       <c r="H27" s="22" t="n">
-        <v>7668.4251</v>
+        <v>68913.8637</v>
       </c>
       <c r="I27" s="22" t="n">
-        <v>63378.2161</v>
+        <v>0</v>
       </c>
       <c r="J27" s="22" t="n">
-        <v>39485.2823</v>
+        <v>2308.6525</v>
       </c>
     </row>
     <row r="28">
@@ -10886,25 +10886,25 @@
         <v>2</v>
       </c>
       <c r="D28" s="22" t="n">
-        <v>96975.68060000001</v>
+        <v>71541.3569</v>
       </c>
       <c r="E28" s="22" t="n">
-        <v>79.17230000000001</v>
+        <v>100</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="G28" s="22" t="n">
-        <v>138.2485</v>
+        <v>1118.4282</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>7730.4786</v>
+        <v>69283.03140000001</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>56965.5967</v>
+        <v>0</v>
       </c>
       <c r="J28" s="22" t="n">
-        <v>32279.6053</v>
+        <v>2258.3254</v>
       </c>
     </row>
     <row r="29">
@@ -10922,25 +10922,25 @@
         <v>3</v>
       </c>
       <c r="D29" s="22" t="n">
-        <v>105350.4328</v>
+        <v>71887.71060000001</v>
       </c>
       <c r="E29" s="22" t="n">
-        <v>77.8049</v>
+        <v>100</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>361</v>
+        <v>0</v>
       </c>
       <c r="G29" s="22" t="n">
-        <v>135.7628</v>
+        <v>1124.7298</v>
       </c>
       <c r="H29" s="22" t="n">
-        <v>7637.1356</v>
+        <v>69645.09970000001</v>
       </c>
       <c r="I29" s="22" t="n">
-        <v>59637.6928</v>
+        <v>0</v>
       </c>
       <c r="J29" s="22" t="n">
-        <v>38075.6044</v>
+        <v>2242.6109</v>
       </c>
     </row>
     <row r="30">
@@ -10958,25 +10958,25 @@
         <v>4</v>
       </c>
       <c r="D30" s="22" t="n">
-        <v>105415.5421</v>
+        <v>71569.466</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>78.13420000000001</v>
+        <v>100</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="G30" s="22" t="n">
-        <v>135.5447</v>
+        <v>1117.9478</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>7592.9429</v>
+        <v>69279.4268</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>59322.4837</v>
+        <v>0</v>
       </c>
       <c r="J30" s="22" t="n">
-        <v>38500.1156</v>
+        <v>2290.0392</v>
       </c>
     </row>
     <row r="31">
@@ -10994,25 +10994,25 @@
         <v>5</v>
       </c>
       <c r="D31" s="22" t="n">
-        <v>108901.6552</v>
+        <v>71528.0781</v>
       </c>
       <c r="E31" s="22" t="n">
-        <v>77.2227</v>
+        <v>100</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="G31" s="22" t="n">
-        <v>138.9913</v>
+        <v>1116.911</v>
       </c>
       <c r="H31" s="22" t="n">
-        <v>7746.4599</v>
+        <v>69259.4195</v>
       </c>
       <c r="I31" s="22" t="n">
-        <v>63954.0188</v>
+        <v>0</v>
       </c>
       <c r="J31" s="22" t="n">
-        <v>37201.1765</v>
+        <v>2268.6586</v>
       </c>
     </row>
     <row r="32">
@@ -11030,25 +11030,25 @@
         <v>1</v>
       </c>
       <c r="D32" s="22" t="n">
-        <v>118007.0031</v>
+        <v>71222.51609999999</v>
       </c>
       <c r="E32" s="22" t="n">
-        <v>78.8481</v>
+        <v>100</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G32" s="22" t="n">
-        <v>139.8643</v>
+        <v>1112.2753</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>7700.6231</v>
+        <v>68913.8637</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>63630.8851</v>
+        <v>0</v>
       </c>
       <c r="J32" s="22" t="n">
-        <v>46675.495</v>
+        <v>2308.6525</v>
       </c>
     </row>
     <row r="33">
@@ -11066,25 +11066,25 @@
         <v>2</v>
       </c>
       <c r="D33" s="22" t="n">
-        <v>120436.4608</v>
+        <v>71541.3569</v>
       </c>
       <c r="E33" s="22" t="n">
-        <v>76.91930000000001</v>
+        <v>100</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="G33" s="22" t="n">
-        <v>137.0769</v>
+        <v>1118.4282</v>
       </c>
       <c r="H33" s="22" t="n">
-        <v>7616.1186</v>
+        <v>69283.03140000001</v>
       </c>
       <c r="I33" s="22" t="n">
-        <v>70663.48669999999</v>
+        <v>0</v>
       </c>
       <c r="J33" s="22" t="n">
-        <v>42156.8555</v>
+        <v>2258.3254</v>
       </c>
     </row>
     <row r="34">
@@ -11102,25 +11102,25 @@
         <v>3</v>
       </c>
       <c r="D34" s="22" t="n">
-        <v>105436.6999</v>
+        <v>71887.71060000001</v>
       </c>
       <c r="E34" s="22" t="n">
-        <v>78.4632</v>
+        <v>100</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="G34" s="22" t="n">
-        <v>139.1988</v>
+        <v>1124.7298</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>7748.7196</v>
+        <v>69645.09970000001</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>57092.521</v>
+        <v>0</v>
       </c>
       <c r="J34" s="22" t="n">
-        <v>40595.4593</v>
+        <v>2242.6109</v>
       </c>
     </row>
     <row r="35">
@@ -11138,25 +11138,25 @@
         <v>4</v>
       </c>
       <c r="D35" s="22" t="n">
-        <v>102136.3529</v>
+        <v>71569.466</v>
       </c>
       <c r="E35" s="22" t="n">
-        <v>78.29559999999999</v>
+        <v>100</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G35" s="22" t="n">
-        <v>137.1612</v>
+        <v>1117.9478</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>7673.3612</v>
+        <v>69279.4268</v>
       </c>
       <c r="I35" s="22" t="n">
-        <v>54652.6901</v>
+        <v>0</v>
       </c>
       <c r="J35" s="22" t="n">
-        <v>39810.3016</v>
+        <v>2290.0392</v>
       </c>
     </row>
     <row r="36">
@@ -11174,25 +11174,25 @@
         <v>5</v>
       </c>
       <c r="D36" s="22" t="n">
-        <v>103722.6197</v>
+        <v>71528.0781</v>
       </c>
       <c r="E36" s="22" t="n">
-        <v>78.9027</v>
+        <v>100</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="G36" s="22" t="n">
-        <v>141.2462</v>
+        <v>1116.911</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>7837.1328</v>
+        <v>69259.4195</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>59238.289</v>
+        <v>0</v>
       </c>
       <c r="J36" s="22" t="n">
-        <v>36647.1979</v>
+        <v>2268.6586</v>
       </c>
     </row>
     <row r="37">
@@ -11210,25 +11210,25 @@
         <v>1</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>121866.5552</v>
+        <v>74091.1056</v>
       </c>
       <c r="E37" s="25" t="n">
-        <v>96.36190000000001</v>
+        <v>100</v>
       </c>
       <c r="F37" s="26" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G37" s="25" t="n">
-        <v>174.1918</v>
+        <v>1110.9595</v>
       </c>
       <c r="H37" s="25" t="n">
-        <v>10590.9909</v>
+        <v>71542.2311</v>
       </c>
       <c r="I37" s="25" t="n">
-        <v>4657.7409</v>
+        <v>0</v>
       </c>
       <c r="J37" s="25" t="n">
-        <v>106617.8234</v>
+        <v>2548.8744</v>
       </c>
     </row>
     <row r="38">
@@ -11246,25 +11246,25 @@
         <v>2</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>122048.4074</v>
+        <v>74854.28350000001</v>
       </c>
       <c r="E38" s="25" t="n">
-        <v>95.8638</v>
+        <v>100</v>
       </c>
       <c r="F38" s="26" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G38" s="25" t="n">
-        <v>175.2642</v>
+        <v>1116.9923</v>
       </c>
       <c r="H38" s="25" t="n">
-        <v>11037.7184</v>
+        <v>72302.3826</v>
       </c>
       <c r="I38" s="25" t="n">
-        <v>6989.3718</v>
+        <v>0</v>
       </c>
       <c r="J38" s="25" t="n">
-        <v>104021.3172</v>
+        <v>2551.9009</v>
       </c>
     </row>
     <row r="39">
@@ -11282,25 +11282,25 @@
         <v>3</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>117461.704</v>
+        <v>74827.39659999999</v>
       </c>
       <c r="E39" s="25" t="n">
-        <v>94.75360000000001</v>
+        <v>100</v>
       </c>
       <c r="F39" s="26" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G39" s="25" t="n">
-        <v>173.8349</v>
+        <v>1123.3581</v>
       </c>
       <c r="H39" s="25" t="n">
-        <v>10683.0161</v>
+        <v>72340.02069999999</v>
       </c>
       <c r="I39" s="25" t="n">
-        <v>5313.9784</v>
+        <v>0</v>
       </c>
       <c r="J39" s="25" t="n">
-        <v>101464.7095</v>
+        <v>2487.376</v>
       </c>
     </row>
     <row r="40">
@@ -11318,25 +11318,25 @@
         <v>4</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>105311.0254</v>
+        <v>74120.912</v>
       </c>
       <c r="E40" s="25" t="n">
-        <v>96.5115</v>
+        <v>100</v>
       </c>
       <c r="F40" s="26" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G40" s="25" t="n">
-        <v>162.5245</v>
+        <v>1116.6576</v>
       </c>
       <c r="H40" s="25" t="n">
-        <v>9967.5273</v>
+        <v>71626.2951</v>
       </c>
       <c r="I40" s="25" t="n">
-        <v>2999.5924</v>
+        <v>0</v>
       </c>
       <c r="J40" s="25" t="n">
-        <v>92343.9057</v>
+        <v>2494.6168</v>
       </c>
     </row>
     <row r="41">
@@ -11354,25 +11354,25 @@
         <v>5</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>118018.3632</v>
+        <v>74352.6569</v>
       </c>
       <c r="E41" s="25" t="n">
-        <v>97.9182</v>
+        <v>100</v>
       </c>
       <c r="F41" s="26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G41" s="25" t="n">
-        <v>185.6364</v>
+        <v>1115.5712</v>
       </c>
       <c r="H41" s="25" t="n">
-        <v>11186.4776</v>
+        <v>71856.1835</v>
       </c>
       <c r="I41" s="25" t="n">
-        <v>1692.4367</v>
+        <v>0</v>
       </c>
       <c r="J41" s="25" t="n">
-        <v>105139.4489</v>
+        <v>2496.4735</v>
       </c>
     </row>
     <row r="42">
@@ -11390,25 +11390,25 @@
         <v>1</v>
       </c>
       <c r="D42" s="22" t="n">
-        <v>172457.0201</v>
+        <v>86478.21520000001</v>
       </c>
       <c r="E42" s="22" t="n">
-        <v>87.7332</v>
+        <v>98.3817</v>
       </c>
       <c r="F42" s="15" t="n">
-        <v>197</v>
+        <v>57</v>
       </c>
       <c r="G42" s="22" t="n">
-        <v>101.3949</v>
+        <v>783.2329999999999</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>7681.5364</v>
+        <v>85132.4179</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>37383.0841</v>
+        <v>639.4973</v>
       </c>
       <c r="J42" s="22" t="n">
-        <v>127392.3995</v>
+        <v>706.3</v>
       </c>
     </row>
     <row r="43">
@@ -11426,25 +11426,25 @@
         <v>2</v>
       </c>
       <c r="D43" s="22" t="n">
-        <v>141098.4488</v>
+        <v>87708.87850000001</v>
       </c>
       <c r="E43" s="22" t="n">
-        <v>88.53</v>
+        <v>98.2529</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>168</v>
+        <v>61</v>
       </c>
       <c r="G43" s="22" t="n">
-        <v>98.85809999999999</v>
+        <v>790.9648</v>
       </c>
       <c r="H43" s="22" t="n">
-        <v>7481.5528</v>
+        <v>86408.8799</v>
       </c>
       <c r="I43" s="22" t="n">
-        <v>28431.8189</v>
+        <v>594.6985</v>
       </c>
       <c r="J43" s="22" t="n">
-        <v>105185.0771</v>
+        <v>705.3</v>
       </c>
     </row>
     <row r="44">
@@ -11462,25 +11462,25 @@
         <v>3</v>
       </c>
       <c r="D44" s="22" t="n">
-        <v>138003.4301</v>
+        <v>88934.33319999999</v>
       </c>
       <c r="E44" s="22" t="n">
-        <v>88.23609999999999</v>
+        <v>97.4089</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="G44" s="22" t="n">
-        <v>94.2833</v>
+        <v>789.7652</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>7035.5682</v>
+        <v>87279.9546</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>23825.2512</v>
+        <v>850.5786000000001</v>
       </c>
       <c r="J44" s="22" t="n">
-        <v>107142.6107</v>
+        <v>803.8</v>
       </c>
     </row>
     <row r="45">
@@ -11498,25 +11498,25 @@
         <v>4</v>
       </c>
       <c r="D45" s="22" t="n">
-        <v>201871.9486</v>
+        <v>86781.33779999999</v>
       </c>
       <c r="E45" s="22" t="n">
-        <v>85.6914</v>
+        <v>97.9254</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>213</v>
+        <v>73</v>
       </c>
       <c r="G45" s="22" t="n">
-        <v>104.3208</v>
+        <v>780.9278</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>8063.6158</v>
+        <v>85209.7997</v>
       </c>
       <c r="I45" s="22" t="n">
-        <v>51556.9552</v>
+        <v>753.6381</v>
       </c>
       <c r="J45" s="22" t="n">
-        <v>142251.3777</v>
+        <v>817.9</v>
       </c>
     </row>
     <row r="46">
@@ -11534,25 +11534,25 @@
         <v>5</v>
       </c>
       <c r="D46" s="22" t="n">
-        <v>221332.851</v>
+        <v>87465.6324</v>
       </c>
       <c r="E46" s="22" t="n">
-        <v>83.4426</v>
+        <v>98.1075</v>
       </c>
       <c r="F46" s="15" t="n">
-        <v>254</v>
+        <v>65</v>
       </c>
       <c r="G46" s="22" t="n">
-        <v>114.3293</v>
+        <v>790.6938</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>9026.059800000001</v>
+        <v>86186.56080000001</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>68411.25260000001</v>
+        <v>592.5716</v>
       </c>
       <c r="J46" s="22" t="n">
-        <v>143895.5387</v>
+        <v>686.5</v>
       </c>
     </row>
     <row r="47">
@@ -11570,25 +11570,25 @@
         <v>1</v>
       </c>
       <c r="D47" s="22" t="n">
-        <v>377078.6918</v>
+        <v>102955.4264</v>
       </c>
       <c r="E47" s="22" t="n">
-        <v>79.0855</v>
+        <v>100</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>483</v>
+        <v>0</v>
       </c>
       <c r="G47" s="22" t="n">
-        <v>238.6066</v>
+        <v>866.0083</v>
       </c>
       <c r="H47" s="22" t="n">
-        <v>29616.8242</v>
+        <v>87084.15270000001</v>
       </c>
       <c r="I47" s="22" t="n">
-        <v>80005.4988</v>
+        <v>0</v>
       </c>
       <c r="J47" s="22" t="n">
-        <v>267456.3687</v>
+        <v>15871.2737</v>
       </c>
     </row>
     <row r="48">
@@ -11606,25 +11606,25 @@
         <v>2</v>
       </c>
       <c r="D48" s="22" t="n">
-        <v>360119.5903</v>
+        <v>101851.7996</v>
       </c>
       <c r="E48" s="22" t="n">
-        <v>77.6995</v>
+        <v>100</v>
       </c>
       <c r="F48" s="15" t="n">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="G48" s="22" t="n">
-        <v>238.8054</v>
+        <v>868.9942</v>
       </c>
       <c r="H48" s="22" t="n">
-        <v>29862.1335</v>
+        <v>87354.1545</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>75802.4829</v>
+        <v>0</v>
       </c>
       <c r="J48" s="22" t="n">
-        <v>254454.9739</v>
+        <v>14497.6452</v>
       </c>
     </row>
     <row r="49">
@@ -11642,25 +11642,25 @@
         <v>3</v>
       </c>
       <c r="D49" s="22" t="n">
-        <v>369436.352</v>
+        <v>106449.1803</v>
       </c>
       <c r="E49" s="22" t="n">
-        <v>79.77200000000001</v>
+        <v>100</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
       <c r="G49" s="22" t="n">
-        <v>240.7034</v>
+        <v>866.292</v>
       </c>
       <c r="H49" s="22" t="n">
-        <v>29904.0965</v>
+        <v>87299.5684</v>
       </c>
       <c r="I49" s="22" t="n">
-        <v>76984.3128</v>
+        <v>0</v>
       </c>
       <c r="J49" s="22" t="n">
-        <v>262547.9428</v>
+        <v>19149.6119</v>
       </c>
     </row>
     <row r="50">
@@ -11678,25 +11678,25 @@
         <v>4</v>
       </c>
       <c r="D50" s="22" t="n">
-        <v>368865.4413</v>
+        <v>103240.1063</v>
       </c>
       <c r="E50" s="22" t="n">
-        <v>79.5592</v>
+        <v>100</v>
       </c>
       <c r="F50" s="15" t="n">
-        <v>458</v>
+        <v>0</v>
       </c>
       <c r="G50" s="22" t="n">
-        <v>242.0356</v>
+        <v>869.2279</v>
       </c>
       <c r="H50" s="22" t="n">
-        <v>29994.9539</v>
+        <v>87482.97629999999</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>79895.882</v>
+        <v>0</v>
       </c>
       <c r="J50" s="22" t="n">
-        <v>258974.6054</v>
+        <v>15757.1301</v>
       </c>
     </row>
     <row r="51">
@@ -11714,25 +11714,25 @@
         <v>5</v>
       </c>
       <c r="D51" s="22" t="n">
-        <v>348535.4485</v>
+        <v>97558.2885</v>
       </c>
       <c r="E51" s="22" t="n">
-        <v>80.05119999999999</v>
+        <v>100</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>451</v>
+        <v>0</v>
       </c>
       <c r="G51" s="22" t="n">
-        <v>236.5355</v>
+        <v>872.0253</v>
       </c>
       <c r="H51" s="22" t="n">
-        <v>29629.3027</v>
+        <v>87568.7078</v>
       </c>
       <c r="I51" s="22" t="n">
-        <v>72640.7724</v>
+        <v>0</v>
       </c>
       <c r="J51" s="22" t="n">
-        <v>246265.3734</v>
+        <v>9989.5807</v>
       </c>
     </row>
     <row r="52">
@@ -11750,25 +11750,25 @@
         <v>1</v>
       </c>
       <c r="D52" s="22" t="n">
-        <v>374573.0088</v>
+        <v>102849.1611</v>
       </c>
       <c r="E52" s="22" t="n">
-        <v>78.9234</v>
+        <v>100</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="G52" s="22" t="n">
-        <v>235.2359</v>
+        <v>866.0083</v>
       </c>
       <c r="H52" s="22" t="n">
-        <v>29324.0208</v>
+        <v>87084.15270000001</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>77669.1298</v>
+        <v>0</v>
       </c>
       <c r="J52" s="22" t="n">
-        <v>267579.8582</v>
+        <v>15765.0084</v>
       </c>
     </row>
     <row r="53">
@@ -11786,25 +11786,25 @@
         <v>2</v>
       </c>
       <c r="D53" s="22" t="n">
-        <v>351724.9921</v>
+        <v>101705.058</v>
       </c>
       <c r="E53" s="22" t="n">
-        <v>80.3947</v>
+        <v>100</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="G53" s="22" t="n">
-        <v>242.3354</v>
+        <v>869.0507</v>
       </c>
       <c r="H53" s="22" t="n">
-        <v>30119.2589</v>
+        <v>87361.2724</v>
       </c>
       <c r="I53" s="22" t="n">
-        <v>75236.3266</v>
+        <v>0</v>
       </c>
       <c r="J53" s="22" t="n">
-        <v>246369.4066</v>
+        <v>14343.7856</v>
       </c>
     </row>
     <row r="54">
@@ -11822,25 +11822,25 @@
         <v>3</v>
       </c>
       <c r="D54" s="22" t="n">
-        <v>368748.8303</v>
+        <v>96861.76489999999</v>
       </c>
       <c r="E54" s="22" t="n">
-        <v>79.5949</v>
+        <v>100</v>
       </c>
       <c r="F54" s="15" t="n">
-        <v>456</v>
+        <v>0</v>
       </c>
       <c r="G54" s="22" t="n">
-        <v>239.0312</v>
+        <v>868.2116</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>29785.7551</v>
+        <v>87197.8183</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>81167.56879999999</v>
+        <v>0</v>
       </c>
       <c r="J54" s="22" t="n">
-        <v>257795.5063</v>
+        <v>9663.946599999999</v>
       </c>
     </row>
     <row r="55">
@@ -11858,25 +11858,25 @@
         <v>4</v>
       </c>
       <c r="D55" s="22" t="n">
-        <v>373302.8933</v>
+        <v>98225.32670000001</v>
       </c>
       <c r="E55" s="22" t="n">
-        <v>78.06870000000001</v>
+        <v>100</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>489</v>
+        <v>0</v>
       </c>
       <c r="G55" s="22" t="n">
-        <v>243.7779</v>
+        <v>869.8886</v>
       </c>
       <c r="H55" s="22" t="n">
-        <v>30102.0927</v>
+        <v>87532.9243</v>
       </c>
       <c r="I55" s="22" t="n">
-        <v>84354.6539</v>
+        <v>0</v>
       </c>
       <c r="J55" s="22" t="n">
-        <v>258846.1466</v>
+        <v>10692.4024</v>
       </c>
     </row>
     <row r="56">
@@ -11894,25 +11894,25 @@
         <v>5</v>
       </c>
       <c r="D56" s="22" t="n">
-        <v>370666.4808</v>
+        <v>107480.9504</v>
       </c>
       <c r="E56" s="22" t="n">
-        <v>79.4789</v>
+        <v>100</v>
       </c>
       <c r="F56" s="15" t="n">
-        <v>468</v>
+        <v>0</v>
       </c>
       <c r="G56" s="22" t="n">
-        <v>237.0723</v>
+        <v>866.6546</v>
       </c>
       <c r="H56" s="22" t="n">
-        <v>29733.4504</v>
+        <v>87273.7571</v>
       </c>
       <c r="I56" s="22" t="n">
-        <v>76607.5922</v>
+        <v>0</v>
       </c>
       <c r="J56" s="22" t="n">
-        <v>264325.4382</v>
+        <v>20207.1932</v>
       </c>
     </row>
     <row r="57">
@@ -11930,25 +11930,25 @@
         <v>1</v>
       </c>
       <c r="D57" s="25" t="n">
-        <v>429086.7279</v>
+        <v>89742.3722</v>
       </c>
       <c r="E57" s="25" t="n">
-        <v>77.9759</v>
+        <v>100</v>
       </c>
       <c r="F57" s="26" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="G57" s="25" t="n">
-        <v>237.9475</v>
+        <v>866.4769</v>
       </c>
       <c r="H57" s="25" t="n">
-        <v>31271.0386</v>
+        <v>85232.6835</v>
       </c>
       <c r="I57" s="25" t="n">
-        <v>114785.5258</v>
+        <v>0</v>
       </c>
       <c r="J57" s="25" t="n">
-        <v>283030.1635</v>
+        <v>4509.6887</v>
       </c>
     </row>
     <row r="58">
@@ -11966,25 +11966,25 @@
         <v>2</v>
       </c>
       <c r="D58" s="25" t="n">
-        <v>440124.7085</v>
+        <v>90851.30809999999</v>
       </c>
       <c r="E58" s="25" t="n">
-        <v>76.1135</v>
+        <v>100</v>
       </c>
       <c r="F58" s="26" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="G58" s="25" t="n">
-        <v>236.2877</v>
+        <v>875.2281</v>
       </c>
       <c r="H58" s="25" t="n">
-        <v>31240.4517</v>
+        <v>86359.15730000001</v>
       </c>
       <c r="I58" s="25" t="n">
-        <v>133807.5892</v>
+        <v>0</v>
       </c>
       <c r="J58" s="25" t="n">
-        <v>275076.6676</v>
+        <v>4492.1508</v>
       </c>
     </row>
     <row r="59">
@@ -12002,25 +12002,25 @@
         <v>3</v>
       </c>
       <c r="D59" s="25" t="n">
-        <v>400036.4539</v>
+        <v>90396.20299999999</v>
       </c>
       <c r="E59" s="25" t="n">
-        <v>77.636</v>
+        <v>100</v>
       </c>
       <c r="F59" s="26" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G59" s="25" t="n">
-        <v>237.2949</v>
+        <v>869.388</v>
       </c>
       <c r="H59" s="25" t="n">
-        <v>31050.1672</v>
+        <v>85845.9296</v>
       </c>
       <c r="I59" s="25" t="n">
-        <v>95809.26300000001</v>
+        <v>0</v>
       </c>
       <c r="J59" s="25" t="n">
-        <v>273177.0237</v>
+        <v>4550.2734</v>
       </c>
     </row>
     <row r="60">
@@ -12038,25 +12038,25 @@
         <v>4</v>
       </c>
       <c r="D60" s="25" t="n">
-        <v>414852.0773</v>
+        <v>90690.21090000001</v>
       </c>
       <c r="E60" s="25" t="n">
-        <v>80.8001</v>
+        <v>100</v>
       </c>
       <c r="F60" s="26" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="G60" s="25" t="n">
-        <v>238.0546</v>
+        <v>871.7315</v>
       </c>
       <c r="H60" s="25" t="n">
-        <v>31057.6365</v>
+        <v>86176.35000000001</v>
       </c>
       <c r="I60" s="25" t="n">
-        <v>111679.9497</v>
+        <v>0</v>
       </c>
       <c r="J60" s="25" t="n">
-        <v>272114.4911</v>
+        <v>4513.8609</v>
       </c>
     </row>
     <row r="61">
@@ -12074,25 +12074,25 @@
         <v>5</v>
       </c>
       <c r="D61" s="25" t="n">
-        <v>404266.6923</v>
+        <v>90137.4388</v>
       </c>
       <c r="E61" s="25" t="n">
-        <v>83.55459999999999</v>
+        <v>100</v>
       </c>
       <c r="F61" s="26" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="G61" s="25" t="n">
-        <v>242.4862</v>
+        <v>866.2306</v>
       </c>
       <c r="H61" s="25" t="n">
-        <v>31810.3584</v>
+        <v>85657.03320000001</v>
       </c>
       <c r="I61" s="25" t="n">
-        <v>87972.0684</v>
+        <v>0</v>
       </c>
       <c r="J61" s="25" t="n">
-        <v>284484.2655</v>
+        <v>4480.4056</v>
       </c>
     </row>
     <row r="62">
@@ -12110,25 +12110,25 @@
         <v>1</v>
       </c>
       <c r="D62" s="22" t="n">
-        <v>180318.6252</v>
+        <v>242821.6799</v>
       </c>
       <c r="E62" s="22" t="n">
-        <v>90.26220000000001</v>
+        <v>90.28360000000001</v>
       </c>
       <c r="F62" s="15" t="n">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="G62" s="22" t="n">
-        <v>116.442</v>
+        <v>109.5747</v>
       </c>
       <c r="H62" s="22" t="n">
-        <v>11985.2351</v>
+        <v>14209.4854</v>
       </c>
       <c r="I62" s="22" t="n">
-        <v>27489.9731</v>
+        <v>29320.0712</v>
       </c>
       <c r="J62" s="22" t="n">
-        <v>140843.417</v>
+        <v>199292.1233</v>
       </c>
     </row>
     <row r="63">
@@ -12146,25 +12146,25 @@
         <v>2</v>
       </c>
       <c r="D63" s="22" t="n">
-        <v>140353.8038</v>
+        <v>176355.9413</v>
       </c>
       <c r="E63" s="22" t="n">
-        <v>92.6118</v>
+        <v>93.0448</v>
       </c>
       <c r="F63" s="15" t="n">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="G63" s="22" t="n">
-        <v>118.9866</v>
+        <v>107.4171</v>
       </c>
       <c r="H63" s="22" t="n">
-        <v>12294.4903</v>
+        <v>13575.3294</v>
       </c>
       <c r="I63" s="22" t="n">
-        <v>17324.597</v>
+        <v>5333.8543</v>
       </c>
       <c r="J63" s="22" t="n">
-        <v>110734.7165</v>
+        <v>157446.7576</v>
       </c>
     </row>
     <row r="64">
@@ -12182,25 +12182,25 @@
         <v>3</v>
       </c>
       <c r="D64" s="22" t="n">
-        <v>162356.8438</v>
+        <v>198850.6062</v>
       </c>
       <c r="E64" s="22" t="n">
-        <v>90.6413</v>
+        <v>90.955</v>
       </c>
       <c r="F64" s="15" t="n">
-        <v>215</v>
+        <v>281</v>
       </c>
       <c r="G64" s="22" t="n">
-        <v>124.9363</v>
+        <v>104.7319</v>
       </c>
       <c r="H64" s="22" t="n">
-        <v>13085.0812</v>
+        <v>13185.4114</v>
       </c>
       <c r="I64" s="22" t="n">
-        <v>26660.5136</v>
+        <v>13499.4521</v>
       </c>
       <c r="J64" s="22" t="n">
-        <v>122611.249</v>
+        <v>172165.7428</v>
       </c>
     </row>
     <row r="65">
@@ -12218,25 +12218,25 @@
         <v>4</v>
       </c>
       <c r="D65" s="22" t="n">
-        <v>177398.4851</v>
+        <v>237832.2153</v>
       </c>
       <c r="E65" s="22" t="n">
-        <v>90.2942</v>
+        <v>90.4213</v>
       </c>
       <c r="F65" s="15" t="n">
-        <v>222</v>
+        <v>281</v>
       </c>
       <c r="G65" s="22" t="n">
-        <v>121.0894</v>
+        <v>107.2442</v>
       </c>
       <c r="H65" s="22" t="n">
-        <v>12681.6351</v>
+        <v>14040.5272</v>
       </c>
       <c r="I65" s="22" t="n">
-        <v>31192.1314</v>
+        <v>23458.226</v>
       </c>
       <c r="J65" s="22" t="n">
-        <v>133524.7186</v>
+        <v>200333.4621</v>
       </c>
     </row>
     <row r="66">
@@ -12254,25 +12254,25 @@
         <v>5</v>
       </c>
       <c r="D66" s="22" t="n">
-        <v>193703.9473</v>
+        <v>211572.6054</v>
       </c>
       <c r="E66" s="22" t="n">
-        <v>89.8002</v>
+        <v>91.5838</v>
       </c>
       <c r="F66" s="15" t="n">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="G66" s="22" t="n">
-        <v>123.2304</v>
+        <v>106.7607</v>
       </c>
       <c r="H66" s="22" t="n">
-        <v>12972.8139</v>
+        <v>13693.6797</v>
       </c>
       <c r="I66" s="22" t="n">
-        <v>34236.7825</v>
+        <v>14921.3617</v>
       </c>
       <c r="J66" s="22" t="n">
-        <v>146494.3509</v>
+        <v>182957.564</v>
       </c>
     </row>
     <row r="67">
@@ -12290,25 +12290,25 @@
         <v>1</v>
       </c>
       <c r="D67" s="22" t="n">
-        <v>229789.9753</v>
+        <v>229867.5525</v>
       </c>
       <c r="E67" s="22" t="n">
-        <v>77.5693</v>
+        <v>77.6019</v>
       </c>
       <c r="F67" s="15" t="n">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="G67" s="22" t="n">
-        <v>116.5994</v>
+        <v>116.4145</v>
       </c>
       <c r="H67" s="22" t="n">
-        <v>14595.0335</v>
+        <v>14577.5028</v>
       </c>
       <c r="I67" s="22" t="n">
-        <v>140652.8437</v>
+        <v>140807.7489</v>
       </c>
       <c r="J67" s="22" t="n">
-        <v>74542.0981</v>
+        <v>74482.3008</v>
       </c>
     </row>
     <row r="68">
@@ -12326,25 +12326,25 @@
         <v>2</v>
       </c>
       <c r="D68" s="22" t="n">
-        <v>196070.6267</v>
+        <v>196040.426</v>
       </c>
       <c r="E68" s="22" t="n">
-        <v>78.4025</v>
+        <v>78.4024</v>
       </c>
       <c r="F68" s="15" t="n">
         <v>752</v>
       </c>
       <c r="G68" s="22" t="n">
-        <v>120.0553</v>
+        <v>120.0539</v>
       </c>
       <c r="H68" s="22" t="n">
-        <v>15083.5655</v>
+        <v>15084.3551</v>
       </c>
       <c r="I68" s="22" t="n">
-        <v>118580.1797</v>
+        <v>118576.5844</v>
       </c>
       <c r="J68" s="22" t="n">
-        <v>62406.8816</v>
+        <v>62379.4864</v>
       </c>
     </row>
     <row r="69">
@@ -12362,7 +12362,7 @@
         <v>3</v>
       </c>
       <c r="D69" s="22" t="n">
-        <v>198388.6974</v>
+        <v>198346.895</v>
       </c>
       <c r="E69" s="22" t="n">
         <v>79.2418</v>
@@ -12371,16 +12371,16 @@
         <v>715</v>
       </c>
       <c r="G69" s="22" t="n">
-        <v>119.3672</v>
+        <v>119.364</v>
       </c>
       <c r="H69" s="22" t="n">
-        <v>14980.3595</v>
+        <v>14980.9873</v>
       </c>
       <c r="I69" s="22" t="n">
-        <v>126007.0036</v>
+        <v>125997.9559</v>
       </c>
       <c r="J69" s="22" t="n">
-        <v>57401.3343</v>
+        <v>57367.9518</v>
       </c>
     </row>
     <row r="70">
@@ -12398,7 +12398,7 @@
         <v>4</v>
       </c>
       <c r="D70" s="22" t="n">
-        <v>205528.0873</v>
+        <v>205480.4653</v>
       </c>
       <c r="E70" s="22" t="n">
         <v>78.23309999999999</v>
@@ -12407,16 +12407,16 @@
         <v>762</v>
       </c>
       <c r="G70" s="22" t="n">
-        <v>118.4062</v>
+        <v>118.4029</v>
       </c>
       <c r="H70" s="22" t="n">
-        <v>14909.9819</v>
+        <v>14910.6102</v>
       </c>
       <c r="I70" s="22" t="n">
-        <v>125605.8517</v>
+        <v>125595.7492</v>
       </c>
       <c r="J70" s="22" t="n">
-        <v>65012.2537</v>
+        <v>64974.1059</v>
       </c>
     </row>
     <row r="71">
@@ -12434,25 +12434,25 @@
         <v>5</v>
       </c>
       <c r="D71" s="22" t="n">
-        <v>219700.0787</v>
+        <v>208567.0754</v>
       </c>
       <c r="E71" s="22" t="n">
-        <v>77.1135</v>
+        <v>77.6506</v>
       </c>
       <c r="F71" s="15" t="n">
-        <v>797</v>
+        <v>777</v>
       </c>
       <c r="G71" s="22" t="n">
-        <v>116.3656</v>
+        <v>116.3522</v>
       </c>
       <c r="H71" s="22" t="n">
-        <v>14644.4357</v>
+        <v>14634.7727</v>
       </c>
       <c r="I71" s="22" t="n">
-        <v>129108.6675</v>
+        <v>126547.0544</v>
       </c>
       <c r="J71" s="22" t="n">
-        <v>75946.97560000001</v>
+        <v>67385.2484</v>
       </c>
     </row>
     <row r="72">
@@ -14990,25 +14990,25 @@
         <v>1</v>
       </c>
       <c r="D142" s="22" t="n">
-        <v>58956.3062</v>
+        <v>91094.1341</v>
       </c>
       <c r="E142" s="22" t="n">
-        <v>95.5762</v>
+        <v>95.62949999999999</v>
       </c>
       <c r="F142" s="15" t="n">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="G142" s="22" t="n">
-        <v>243.8392</v>
+        <v>231.2646</v>
       </c>
       <c r="H142" s="22" t="n">
-        <v>23704.0311</v>
+        <v>25051.1361</v>
       </c>
       <c r="I142" s="22" t="n">
-        <v>1672.0983</v>
+        <v>1830.1285</v>
       </c>
       <c r="J142" s="22" t="n">
-        <v>33580.1769</v>
+        <v>64212.8695</v>
       </c>
     </row>
     <row r="143">
@@ -15026,25 +15026,25 @@
         <v>2</v>
       </c>
       <c r="D143" s="22" t="n">
-        <v>50587.1456</v>
+        <v>75904.46309999999</v>
       </c>
       <c r="E143" s="22" t="n">
-        <v>95.3322</v>
+        <v>95.7775</v>
       </c>
       <c r="F143" s="15" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G143" s="22" t="n">
-        <v>249.44</v>
+        <v>236.5716</v>
       </c>
       <c r="H143" s="22" t="n">
-        <v>24257.1162</v>
+        <v>25635.8489</v>
       </c>
       <c r="I143" s="22" t="n">
-        <v>1768.2438</v>
+        <v>1729.1913</v>
       </c>
       <c r="J143" s="22" t="n">
-        <v>24561.7857</v>
+        <v>48539.423</v>
       </c>
     </row>
     <row r="144">
@@ -15062,25 +15062,25 @@
         <v>3</v>
       </c>
       <c r="D144" s="22" t="n">
-        <v>61850.6107</v>
+        <v>86250.1795</v>
       </c>
       <c r="E144" s="22" t="n">
-        <v>95.3229</v>
+        <v>95.12309999999999</v>
       </c>
       <c r="F144" s="15" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="G144" s="22" t="n">
-        <v>248.7222</v>
+        <v>237.3472</v>
       </c>
       <c r="H144" s="22" t="n">
-        <v>24186.0079</v>
+        <v>25727.8591</v>
       </c>
       <c r="I144" s="22" t="n">
-        <v>1897.7638</v>
+        <v>1939.0192</v>
       </c>
       <c r="J144" s="22" t="n">
-        <v>35766.839</v>
+        <v>58583.3012</v>
       </c>
     </row>
     <row r="145">
@@ -15098,25 +15098,25 @@
         <v>4</v>
       </c>
       <c r="D145" s="22" t="n">
-        <v>60325.818</v>
+        <v>82424.38</v>
       </c>
       <c r="E145" s="22" t="n">
-        <v>95.6919</v>
+        <v>95.2419</v>
       </c>
       <c r="F145" s="15" t="n">
-        <v>169</v>
+        <v>206</v>
       </c>
       <c r="G145" s="22" t="n">
-        <v>246.7068</v>
+        <v>235.978</v>
       </c>
       <c r="H145" s="22" t="n">
-        <v>24022.3414</v>
+        <v>25516.2312</v>
       </c>
       <c r="I145" s="22" t="n">
-        <v>1602.8759</v>
+        <v>1762.0979</v>
       </c>
       <c r="J145" s="22" t="n">
-        <v>34700.6006</v>
+        <v>55146.0509</v>
       </c>
     </row>
     <row r="146">
@@ -15134,25 +15134,25 @@
         <v>5</v>
       </c>
       <c r="D146" s="22" t="n">
-        <v>49694.5595</v>
+        <v>107924.222</v>
       </c>
       <c r="E146" s="22" t="n">
-        <v>95.48399999999999</v>
+        <v>94.7341</v>
       </c>
       <c r="F146" s="15" t="n">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="G146" s="22" t="n">
-        <v>248.9538</v>
+        <v>230.1917</v>
       </c>
       <c r="H146" s="22" t="n">
-        <v>24282.8765</v>
+        <v>24945.5125</v>
       </c>
       <c r="I146" s="22" t="n">
-        <v>1604.9903</v>
+        <v>2159.6935</v>
       </c>
       <c r="J146" s="22" t="n">
-        <v>23806.6927</v>
+        <v>80819.016</v>
       </c>
     </row>
     <row r="147">
@@ -15710,25 +15710,25 @@
         <v>1</v>
       </c>
       <c r="D162" s="22" t="n">
-        <v>312687.7597</v>
+        <v>130513.2153</v>
       </c>
       <c r="E162" s="22" t="n">
-        <v>90.4658</v>
+        <v>95.9562</v>
       </c>
       <c r="F162" s="15" t="n">
-        <v>458</v>
+        <v>354</v>
       </c>
       <c r="G162" s="22" t="n">
-        <v>117.2202</v>
+        <v>355.3229</v>
       </c>
       <c r="H162" s="22" t="n">
-        <v>24178.0265</v>
+        <v>95685.4222</v>
       </c>
       <c r="I162" s="22" t="n">
-        <v>38886.9232</v>
+        <v>3785.556</v>
       </c>
       <c r="J162" s="22" t="n">
-        <v>249622.8099</v>
+        <v>31042.2371</v>
       </c>
     </row>
     <row r="163">
@@ -15746,25 +15746,25 @@
         <v>2</v>
       </c>
       <c r="D163" s="22" t="n">
-        <v>326628.6902</v>
+        <v>133707.3694</v>
       </c>
       <c r="E163" s="22" t="n">
-        <v>90.337</v>
+        <v>96.3986</v>
       </c>
       <c r="F163" s="15" t="n">
-        <v>463</v>
+        <v>319</v>
       </c>
       <c r="G163" s="22" t="n">
-        <v>118.7195</v>
+        <v>357.5219</v>
       </c>
       <c r="H163" s="22" t="n">
-        <v>24604.6634</v>
+        <v>97024.2185</v>
       </c>
       <c r="I163" s="22" t="n">
-        <v>41706.7787</v>
+        <v>3617.0668</v>
       </c>
       <c r="J163" s="22" t="n">
-        <v>260317.2481</v>
+        <v>33066.0841</v>
       </c>
     </row>
     <row r="164">
@@ -15782,25 +15782,25 @@
         <v>3</v>
       </c>
       <c r="D164" s="22" t="n">
-        <v>332439.9403</v>
+        <v>164769.9105</v>
       </c>
       <c r="E164" s="22" t="n">
-        <v>91.527</v>
+        <v>95.318</v>
       </c>
       <c r="F164" s="15" t="n">
-        <v>435</v>
+        <v>372</v>
       </c>
       <c r="G164" s="22" t="n">
-        <v>121.8667</v>
+        <v>355.452</v>
       </c>
       <c r="H164" s="22" t="n">
-        <v>25320.2109</v>
+        <v>96148.3976</v>
       </c>
       <c r="I164" s="22" t="n">
-        <v>33721.0431</v>
+        <v>7774.6855</v>
       </c>
       <c r="J164" s="22" t="n">
-        <v>273398.6862</v>
+        <v>60846.8275</v>
       </c>
     </row>
     <row r="165">
@@ -15818,25 +15818,25 @@
         <v>4</v>
       </c>
       <c r="D165" s="22" t="n">
-        <v>354370.8627</v>
+        <v>153701.0498</v>
       </c>
       <c r="E165" s="22" t="n">
-        <v>90.57380000000001</v>
+        <v>95.61669999999999</v>
       </c>
       <c r="F165" s="15" t="n">
-        <v>438</v>
+        <v>377</v>
       </c>
       <c r="G165" s="22" t="n">
-        <v>123.9024</v>
+        <v>356.1907</v>
       </c>
       <c r="H165" s="22" t="n">
-        <v>25977.0868</v>
+        <v>96858.1819</v>
       </c>
       <c r="I165" s="22" t="n">
-        <v>60531.9978</v>
+        <v>5592.0162</v>
       </c>
       <c r="J165" s="22" t="n">
-        <v>267861.7781</v>
+        <v>51250.8517</v>
       </c>
     </row>
     <row r="166">
@@ -15854,25 +15854,25 @@
         <v>5</v>
       </c>
       <c r="D166" s="22" t="n">
-        <v>336214.158</v>
+        <v>130563.2913</v>
       </c>
       <c r="E166" s="22" t="n">
-        <v>91.2277</v>
+        <v>96.16079999999999</v>
       </c>
       <c r="F166" s="15" t="n">
-        <v>432</v>
+        <v>339</v>
       </c>
       <c r="G166" s="22" t="n">
-        <v>117.2283</v>
+        <v>354.4201</v>
       </c>
       <c r="H166" s="22" t="n">
-        <v>24133.1858</v>
+        <v>95921.76850000001</v>
       </c>
       <c r="I166" s="22" t="n">
-        <v>49354.6807</v>
+        <v>3496.3776</v>
       </c>
       <c r="J166" s="22" t="n">
-        <v>262726.2915</v>
+        <v>31145.1452</v>
       </c>
     </row>
     <row r="167">
@@ -15890,25 +15890,25 @@
         <v>1</v>
       </c>
       <c r="D167" s="22" t="n">
-        <v>433321.3997</v>
+        <v>116837.8564</v>
       </c>
       <c r="E167" s="22" t="n">
-        <v>77.678</v>
+        <v>99.43980000000001</v>
       </c>
       <c r="F167" s="15" t="n">
-        <v>1557</v>
+        <v>40</v>
       </c>
       <c r="G167" s="22" t="n">
-        <v>124.6754</v>
+        <v>405.8533</v>
       </c>
       <c r="H167" s="22" t="n">
-        <v>30544.0267</v>
+        <v>105369.7167</v>
       </c>
       <c r="I167" s="22" t="n">
-        <v>277158.8815</v>
+        <v>1721.705</v>
       </c>
       <c r="J167" s="22" t="n">
-        <v>125618.4916</v>
+        <v>9746.4347</v>
       </c>
     </row>
     <row r="168">
@@ -15926,25 +15926,25 @@
         <v>2</v>
       </c>
       <c r="D168" s="22" t="n">
-        <v>417050.5175</v>
+        <v>117781.2529</v>
       </c>
       <c r="E168" s="22" t="n">
-        <v>78.00790000000001</v>
+        <v>99.0368</v>
       </c>
       <c r="F168" s="15" t="n">
-        <v>1511</v>
+        <v>68</v>
       </c>
       <c r="G168" s="22" t="n">
-        <v>124.8544</v>
+        <v>406.3892</v>
       </c>
       <c r="H168" s="22" t="n">
-        <v>30643.3954</v>
+        <v>105605.7066</v>
       </c>
       <c r="I168" s="22" t="n">
-        <v>265653.3715</v>
+        <v>2438.5688</v>
       </c>
       <c r="J168" s="22" t="n">
-        <v>120753.7506</v>
+        <v>9736.977500000001</v>
       </c>
     </row>
     <row r="169">
@@ -15962,25 +15962,25 @@
         <v>3</v>
       </c>
       <c r="D169" s="22" t="n">
-        <v>421810.2437</v>
+        <v>116351.7926</v>
       </c>
       <c r="E169" s="22" t="n">
-        <v>77.5527</v>
+        <v>99.3366</v>
       </c>
       <c r="F169" s="15" t="n">
-        <v>1565</v>
+        <v>47</v>
       </c>
       <c r="G169" s="22" t="n">
-        <v>124.3632</v>
+        <v>405.7816</v>
       </c>
       <c r="H169" s="22" t="n">
-        <v>30679.1152</v>
+        <v>105460.3547</v>
       </c>
       <c r="I169" s="22" t="n">
-        <v>272395.4627</v>
+        <v>1162.4049</v>
       </c>
       <c r="J169" s="22" t="n">
-        <v>118735.6659</v>
+        <v>9729.032999999999</v>
       </c>
     </row>
     <row r="170">
@@ -15998,25 +15998,25 @@
         <v>4</v>
       </c>
       <c r="D170" s="22" t="n">
-        <v>428695.4573</v>
+        <v>116795.6408</v>
       </c>
       <c r="E170" s="22" t="n">
-        <v>77.2212</v>
+        <v>99.1656</v>
       </c>
       <c r="F170" s="15" t="n">
-        <v>1594</v>
+        <v>59</v>
       </c>
       <c r="G170" s="22" t="n">
-        <v>122.7897</v>
+        <v>405.5334</v>
       </c>
       <c r="H170" s="22" t="n">
-        <v>30352.157</v>
+        <v>105371.9996</v>
       </c>
       <c r="I170" s="22" t="n">
-        <v>288301.6449</v>
+        <v>1674.5382</v>
       </c>
       <c r="J170" s="22" t="n">
-        <v>110041.6554</v>
+        <v>9749.102999999999</v>
       </c>
     </row>
     <row r="171">
@@ -16034,25 +16034,25 @@
         <v>5</v>
       </c>
       <c r="D171" s="22" t="n">
-        <v>454202.4892</v>
+        <v>116377.9797</v>
       </c>
       <c r="E171" s="22" t="n">
-        <v>77.4824</v>
+        <v>99.7106</v>
       </c>
       <c r="F171" s="15" t="n">
-        <v>1579</v>
+        <v>21</v>
       </c>
       <c r="G171" s="22" t="n">
-        <v>123.862</v>
+        <v>408.7379</v>
       </c>
       <c r="H171" s="22" t="n">
-        <v>30295.1442</v>
+        <v>106144.6314</v>
       </c>
       <c r="I171" s="22" t="n">
-        <v>291689.2541</v>
+        <v>466.4295</v>
       </c>
       <c r="J171" s="22" t="n">
-        <v>132218.0909</v>
+        <v>9766.918799999999</v>
       </c>
     </row>
     <row r="172">
@@ -16070,25 +16070,25 @@
         <v>1</v>
       </c>
       <c r="D172" s="22" t="n">
-        <v>422138.1299</v>
+        <v>116837.8564</v>
       </c>
       <c r="E172" s="22" t="n">
-        <v>77.52500000000001</v>
+        <v>99.43980000000001</v>
       </c>
       <c r="F172" s="15" t="n">
-        <v>1562</v>
+        <v>40</v>
       </c>
       <c r="G172" s="22" t="n">
-        <v>124.1079</v>
+        <v>405.8533</v>
       </c>
       <c r="H172" s="22" t="n">
-        <v>30411.0604</v>
+        <v>105369.7167</v>
       </c>
       <c r="I172" s="22" t="n">
-        <v>273949.4048</v>
+        <v>1721.705</v>
       </c>
       <c r="J172" s="22" t="n">
-        <v>117777.6646</v>
+        <v>9746.4347</v>
       </c>
     </row>
     <row r="173">
@@ -16106,25 +16106,25 @@
         <v>2</v>
       </c>
       <c r="D173" s="22" t="n">
-        <v>395627.3329</v>
+        <v>117781.2529</v>
       </c>
       <c r="E173" s="22" t="n">
-        <v>77.6561</v>
+        <v>99.0368</v>
       </c>
       <c r="F173" s="15" t="n">
-        <v>1555</v>
+        <v>68</v>
       </c>
       <c r="G173" s="22" t="n">
-        <v>123.4153</v>
+        <v>406.3892</v>
       </c>
       <c r="H173" s="22" t="n">
-        <v>30356.3358</v>
+        <v>105605.7066</v>
       </c>
       <c r="I173" s="22" t="n">
-        <v>260446.2886</v>
+        <v>2438.5688</v>
       </c>
       <c r="J173" s="22" t="n">
-        <v>104824.7085</v>
+        <v>9736.977500000001</v>
       </c>
     </row>
     <row r="174">
@@ -16142,25 +16142,25 @@
         <v>3</v>
       </c>
       <c r="D174" s="22" t="n">
-        <v>393598.7179</v>
+        <v>116351.7926</v>
       </c>
       <c r="E174" s="22" t="n">
-        <v>77.9152</v>
+        <v>99.3366</v>
       </c>
       <c r="F174" s="15" t="n">
-        <v>1537</v>
+        <v>47</v>
       </c>
       <c r="G174" s="22" t="n">
-        <v>123.5571</v>
+        <v>405.7816</v>
       </c>
       <c r="H174" s="22" t="n">
-        <v>30505.4344</v>
+        <v>105460.3547</v>
       </c>
       <c r="I174" s="22" t="n">
-        <v>251788.64</v>
+        <v>1162.4049</v>
       </c>
       <c r="J174" s="22" t="n">
-        <v>111304.6435</v>
+        <v>9729.032999999999</v>
       </c>
     </row>
     <row r="175">
@@ -16178,25 +16178,25 @@
         <v>4</v>
       </c>
       <c r="D175" s="22" t="n">
-        <v>432993.4564</v>
+        <v>116795.6408</v>
       </c>
       <c r="E175" s="22" t="n">
-        <v>77.75360000000001</v>
+        <v>99.1656</v>
       </c>
       <c r="F175" s="15" t="n">
-        <v>1546</v>
+        <v>59</v>
       </c>
       <c r="G175" s="22" t="n">
-        <v>127.3484</v>
+        <v>405.5334</v>
       </c>
       <c r="H175" s="22" t="n">
-        <v>31289.4577</v>
+        <v>105371.9996</v>
       </c>
       <c r="I175" s="22" t="n">
-        <v>282379.885</v>
+        <v>1674.5382</v>
       </c>
       <c r="J175" s="22" t="n">
-        <v>119324.1136</v>
+        <v>9749.102999999999</v>
       </c>
     </row>
     <row r="176">
@@ -16214,25 +16214,25 @@
         <v>5</v>
       </c>
       <c r="D176" s="22" t="n">
-        <v>412782.9307</v>
+        <v>116377.9797</v>
       </c>
       <c r="E176" s="22" t="n">
-        <v>77.488</v>
+        <v>99.7106</v>
       </c>
       <c r="F176" s="15" t="n">
-        <v>1573</v>
+        <v>21</v>
       </c>
       <c r="G176" s="22" t="n">
-        <v>122.8826</v>
+        <v>408.7379</v>
       </c>
       <c r="H176" s="22" t="n">
-        <v>30170.6481</v>
+        <v>106144.6314</v>
       </c>
       <c r="I176" s="22" t="n">
-        <v>271192.607</v>
+        <v>466.4295</v>
       </c>
       <c r="J176" s="22" t="n">
-        <v>111419.6756</v>
+        <v>9766.918799999999</v>
       </c>
     </row>
     <row r="177">
@@ -16250,25 +16250,25 @@
         <v>1</v>
       </c>
       <c r="D177" s="25" t="n">
-        <v>394457.9912</v>
+        <v>129473.9262</v>
       </c>
       <c r="E177" s="25" t="n">
-        <v>83.94750000000001</v>
+        <v>99.8437</v>
       </c>
       <c r="F177" s="26" t="n">
-        <v>986</v>
+        <v>11</v>
       </c>
       <c r="G177" s="25" t="n">
-        <v>119.19</v>
+        <v>405.0637</v>
       </c>
       <c r="H177" s="25" t="n">
-        <v>35328.0914</v>
+        <v>113428.1756</v>
       </c>
       <c r="I177" s="25" t="n">
-        <v>214548.499</v>
+        <v>1023.0911</v>
       </c>
       <c r="J177" s="25" t="n">
-        <v>144581.4007</v>
+        <v>15022.6596</v>
       </c>
     </row>
     <row r="178">
@@ -16286,25 +16286,25 @@
         <v>2</v>
       </c>
       <c r="D178" s="25" t="n">
-        <v>394727.9485</v>
+        <v>123292.9924</v>
       </c>
       <c r="E178" s="25" t="n">
-        <v>84.7585</v>
+        <v>99.92610000000001</v>
       </c>
       <c r="F178" s="26" t="n">
-        <v>927</v>
+        <v>5</v>
       </c>
       <c r="G178" s="25" t="n">
-        <v>121.2944</v>
+        <v>404.8383</v>
       </c>
       <c r="H178" s="25" t="n">
-        <v>35288.4972</v>
+        <v>112776.4864</v>
       </c>
       <c r="I178" s="25" t="n">
-        <v>218737.111</v>
+        <v>108.6052</v>
       </c>
       <c r="J178" s="25" t="n">
-        <v>140702.3403</v>
+        <v>10407.9008</v>
       </c>
     </row>
     <row r="179">
@@ -16322,25 +16322,25 @@
         <v>3</v>
       </c>
       <c r="D179" s="25" t="n">
-        <v>385035.8557</v>
+        <v>128496.7575</v>
       </c>
       <c r="E179" s="25" t="n">
-        <v>83.53489999999999</v>
+        <v>99.5539</v>
       </c>
       <c r="F179" s="26" t="n">
-        <v>996</v>
+        <v>32</v>
       </c>
       <c r="G179" s="25" t="n">
-        <v>116.6828</v>
+        <v>407.0479</v>
       </c>
       <c r="H179" s="25" t="n">
-        <v>35184.3719</v>
+        <v>114399.5573</v>
       </c>
       <c r="I179" s="25" t="n">
-        <v>201587.8826</v>
+        <v>3925.2454</v>
       </c>
       <c r="J179" s="25" t="n">
-        <v>148263.6011</v>
+        <v>10171.9549</v>
       </c>
     </row>
     <row r="180">
@@ -16358,25 +16358,25 @@
         <v>4</v>
       </c>
       <c r="D180" s="25" t="n">
-        <v>375159.0032</v>
+        <v>131729.2231</v>
       </c>
       <c r="E180" s="25" t="n">
-        <v>85.3229</v>
+        <v>99.5566</v>
       </c>
       <c r="F180" s="26" t="n">
-        <v>871</v>
+        <v>32</v>
       </c>
       <c r="G180" s="25" t="n">
-        <v>119.3977</v>
+        <v>404.6365</v>
       </c>
       <c r="H180" s="25" t="n">
-        <v>35264.9612</v>
+        <v>112846.028</v>
       </c>
       <c r="I180" s="25" t="n">
-        <v>193257.6768</v>
+        <v>2483.5826</v>
       </c>
       <c r="J180" s="25" t="n">
-        <v>146636.3653</v>
+        <v>16399.6125</v>
       </c>
     </row>
     <row r="181">
@@ -16394,25 +16394,25 @@
         <v>5</v>
       </c>
       <c r="D181" s="25" t="n">
-        <v>392409.7279</v>
+        <v>127961.5365</v>
       </c>
       <c r="E181" s="25" t="n">
-        <v>83.8018</v>
+        <v>99.9567</v>
       </c>
       <c r="F181" s="26" t="n">
-        <v>979</v>
+        <v>3</v>
       </c>
       <c r="G181" s="25" t="n">
-        <v>119.3294</v>
+        <v>409.0521</v>
       </c>
       <c r="H181" s="25" t="n">
-        <v>35511.4806</v>
+        <v>114139.6389</v>
       </c>
       <c r="I181" s="25" t="n">
-        <v>206065.3711</v>
+        <v>8.217000000000001</v>
       </c>
       <c r="J181" s="25" t="n">
-        <v>150832.8762</v>
+        <v>13813.6807</v>
       </c>
     </row>
     <row r="182">
@@ -16430,25 +16430,25 @@
         <v>1</v>
       </c>
       <c r="D182" s="22" t="n">
-        <v>605454.5876</v>
+        <v>723205.2716</v>
       </c>
       <c r="E182" s="22" t="n">
-        <v>88.8329</v>
+        <v>88.1485</v>
       </c>
       <c r="F182" s="15" t="n">
-        <v>662</v>
+        <v>767</v>
       </c>
       <c r="G182" s="22" t="n">
-        <v>101.3015</v>
+        <v>100.1344</v>
       </c>
       <c r="H182" s="22" t="n">
-        <v>31026.0548</v>
+        <v>34728.0468</v>
       </c>
       <c r="I182" s="22" t="n">
-        <v>137282.1617</v>
+        <v>157533.6655</v>
       </c>
       <c r="J182" s="22" t="n">
-        <v>437146.3711</v>
+        <v>530943.5594</v>
       </c>
     </row>
     <row r="183">
@@ -16466,25 +16466,25 @@
         <v>2</v>
       </c>
       <c r="D183" s="22" t="n">
-        <v>621754.3159</v>
+        <v>835505.7077</v>
       </c>
       <c r="E183" s="22" t="n">
-        <v>88.3032</v>
+        <v>85.253</v>
       </c>
       <c r="F183" s="15" t="n">
-        <v>710</v>
+        <v>963</v>
       </c>
       <c r="G183" s="22" t="n">
-        <v>100.5524</v>
+        <v>101.4147</v>
       </c>
       <c r="H183" s="22" t="n">
-        <v>30619.9226</v>
+        <v>36465.5092</v>
       </c>
       <c r="I183" s="22" t="n">
-        <v>139826.0592</v>
+        <v>217361.8273</v>
       </c>
       <c r="J183" s="22" t="n">
-        <v>451308.3341</v>
+        <v>581678.3712000001</v>
       </c>
     </row>
     <row r="184">
@@ -16502,25 +16502,25 @@
         <v>3</v>
       </c>
       <c r="D184" s="22" t="n">
-        <v>719477.4534999999</v>
+        <v>678299.7057</v>
       </c>
       <c r="E184" s="22" t="n">
-        <v>87.06</v>
+        <v>89.0971</v>
       </c>
       <c r="F184" s="15" t="n">
-        <v>762</v>
+        <v>720</v>
       </c>
       <c r="G184" s="22" t="n">
-        <v>98.4474</v>
+        <v>93.8997</v>
       </c>
       <c r="H184" s="22" t="n">
-        <v>29977.2784</v>
+        <v>31987.17</v>
       </c>
       <c r="I184" s="22" t="n">
-        <v>172368.9243</v>
+        <v>121235.1771</v>
       </c>
       <c r="J184" s="22" t="n">
-        <v>517131.2509</v>
+        <v>525077.3585</v>
       </c>
     </row>
     <row r="185">
@@ -16538,25 +16538,25 @@
         <v>4</v>
       </c>
       <c r="D185" s="22" t="n">
-        <v>731779.3631</v>
+        <v>755239.8382</v>
       </c>
       <c r="E185" s="22" t="n">
-        <v>87.4777</v>
+        <v>87.4768</v>
       </c>
       <c r="F185" s="15" t="n">
-        <v>743</v>
+        <v>806</v>
       </c>
       <c r="G185" s="22" t="n">
-        <v>100.3913</v>
+        <v>100.7121</v>
       </c>
       <c r="H185" s="22" t="n">
-        <v>30568.9019</v>
+        <v>35055.9816</v>
       </c>
       <c r="I185" s="22" t="n">
-        <v>158905.5147</v>
+        <v>166648.3894</v>
       </c>
       <c r="J185" s="22" t="n">
-        <v>542304.9464</v>
+        <v>553535.4671</v>
       </c>
     </row>
     <row r="186">
@@ -16574,25 +16574,25 @@
         <v>5</v>
       </c>
       <c r="D186" s="22" t="n">
-        <v>705978.0425</v>
+        <v>721214.3317</v>
       </c>
       <c r="E186" s="22" t="n">
-        <v>86.8806</v>
+        <v>87.38890000000001</v>
       </c>
       <c r="F186" s="15" t="n">
-        <v>771</v>
+        <v>817</v>
       </c>
       <c r="G186" s="22" t="n">
-        <v>96.1895</v>
+        <v>98.116</v>
       </c>
       <c r="H186" s="22" t="n">
-        <v>29148.8132</v>
+        <v>34191.2182</v>
       </c>
       <c r="I186" s="22" t="n">
-        <v>163723.7242</v>
+        <v>162634.4212</v>
       </c>
       <c r="J186" s="22" t="n">
-        <v>513105.5051</v>
+        <v>524388.6923</v>
       </c>
     </row>
     <row r="187">
